--- a/FeatureImportance_Results.xlsx
+++ b/FeatureImportance_Results.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="1430" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="2075" uniqueCount="28">
   <si>
     <t>Modelo</t>
   </si>
@@ -77,6 +77,27 @@
   <si>
     <t>Importancia</t>
   </si>
+  <si>
+    <t>dPMax</t>
+  </si>
+  <si>
+    <t>TRelativoVmax</t>
+  </si>
+  <si>
+    <t>dVMax</t>
+  </si>
+  <si>
+    <t>TRelativoRmax</t>
+  </si>
+  <si>
+    <t>dIMax</t>
+  </si>
+  <si>
+    <t>TRelativoImax</t>
+  </si>
+  <si>
+    <t>dRMax</t>
+  </si>
 </sst>
 </file>
 
@@ -153,16 +174,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="0">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C2" s="0">
-        <v>0.90899840850055391</v>
+        <v>0.90080428532531853</v>
       </c>
       <c r="D2" s="0" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E2" s="0">
-        <v>128.38110056329859</v>
+        <v>105.03860033326735</v>
       </c>
     </row>
     <row r="3">
@@ -170,16 +191,16 @@
         <v>1</v>
       </c>
       <c r="B3" s="0">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C3" s="0">
-        <v>0.90899840850055391</v>
+        <v>0.90080428532531853</v>
       </c>
       <c r="D3" s="0" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E3" s="0">
-        <v>102.70028036252535</v>
+        <v>101.58837124307279</v>
       </c>
     </row>
     <row r="4">
@@ -187,16 +208,16 @@
         <v>1</v>
       </c>
       <c r="B4" s="0">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C4" s="0">
-        <v>0.90899840850055391</v>
+        <v>0.90080428532531853</v>
       </c>
       <c r="D4" s="0" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E4" s="0">
-        <v>95.874442990539919</v>
+        <v>95.762856543630846</v>
       </c>
     </row>
     <row r="5">
@@ -204,16 +225,16 @@
         <v>1</v>
       </c>
       <c r="B5" s="0">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C5" s="0">
-        <v>0.90899840850055391</v>
+        <v>0.90080428532531853</v>
       </c>
       <c r="D5" s="0" t="s">
         <v>9</v>
       </c>
       <c r="E5" s="0">
-        <v>72.405808980250683</v>
+        <v>71.033085035544445</v>
       </c>
     </row>
     <row r="6">
@@ -221,16 +242,16 @@
         <v>1</v>
       </c>
       <c r="B6" s="0">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C6" s="0">
-        <v>0.90899840850055391</v>
+        <v>0.90080428532531853</v>
       </c>
       <c r="D6" s="0" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="E6" s="0">
-        <v>35.947111554643705</v>
+        <v>40.403013488757573</v>
       </c>
     </row>
     <row r="7">
@@ -238,16 +259,16 @@
         <v>1</v>
       </c>
       <c r="B7" s="0">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C7" s="0">
-        <v>0.90899840850055391</v>
+        <v>0.90080428532531853</v>
       </c>
       <c r="D7" s="0" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E7" s="0">
-        <v>4.3524743865411866</v>
+        <v>15.103396136922974</v>
       </c>
     </row>
     <row r="8">
@@ -255,16 +276,16 @@
         <v>1</v>
       </c>
       <c r="B8" s="0">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C8" s="0">
-        <v>0.90899840850055391</v>
+        <v>0.90080428532531853</v>
       </c>
       <c r="D8" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="E8" s="0">
-        <v>3.470597317584228</v>
+        <v>14.655066751367508</v>
       </c>
     </row>
     <row r="9">
@@ -272,16 +293,16 @@
         <v>1</v>
       </c>
       <c r="B9" s="0">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C9" s="0">
-        <v>0.90899840850055391</v>
+        <v>0.90080428532531853</v>
       </c>
       <c r="D9" s="0" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E9" s="0">
-        <v>3.2474125879288507</v>
+        <v>7.9130527791816947</v>
       </c>
     </row>
     <row r="10">
@@ -289,16 +310,16 @@
         <v>1</v>
       </c>
       <c r="B10" s="0">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C10" s="0">
-        <v>0.90899840850055391</v>
+        <v>0.90080428532531853</v>
       </c>
       <c r="D10" s="0" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E10" s="0">
-        <v>2.9212637759767386</v>
+        <v>3.5183455784493676</v>
       </c>
     </row>
     <row r="11">
@@ -306,16 +327,16 @@
         <v>1</v>
       </c>
       <c r="B11" s="0">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C11" s="0">
-        <v>0.90899840850055391</v>
+        <v>0.90080428532531853</v>
       </c>
       <c r="D11" s="0" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E11" s="0">
-        <v>2.2930352340522671</v>
+        <v>2.9911315551589568</v>
       </c>
     </row>
     <row r="12">
@@ -323,16 +344,16 @@
         <v>1</v>
       </c>
       <c r="B12" s="0">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C12" s="0">
-        <v>0.92024047570868217</v>
+        <v>0.9081448328068078</v>
       </c>
       <c r="D12" s="0" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E12" s="0">
-        <v>131.12860743588317</v>
+        <v>129.81474176704714</v>
       </c>
     </row>
     <row r="13">
@@ -340,16 +361,16 @@
         <v>1</v>
       </c>
       <c r="B13" s="0">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C13" s="0">
-        <v>0.92024047570868217</v>
+        <v>0.9081448328068078</v>
       </c>
       <c r="D13" s="0" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E13" s="0">
-        <v>130.73711988378378</v>
+        <v>100.55001975715574</v>
       </c>
     </row>
     <row r="14">
@@ -357,16 +378,16 @@
         <v>1</v>
       </c>
       <c r="B14" s="0">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C14" s="0">
-        <v>0.92024047570868217</v>
+        <v>0.9081448328068078</v>
       </c>
       <c r="D14" s="0" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E14" s="0">
-        <v>85.267838145183774</v>
+        <v>85.817507384906989</v>
       </c>
     </row>
     <row r="15">
@@ -374,16 +395,16 @@
         <v>1</v>
       </c>
       <c r="B15" s="0">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C15" s="0">
-        <v>0.92024047570868217</v>
+        <v>0.9081448328068078</v>
       </c>
       <c r="D15" s="0" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E15" s="0">
-        <v>77.397351558589762</v>
+        <v>60.551997382895287</v>
       </c>
     </row>
     <row r="16">
@@ -391,16 +412,16 @@
         <v>1</v>
       </c>
       <c r="B16" s="0">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C16" s="0">
-        <v>0.92024047570868217</v>
+        <v>0.9081448328068078</v>
       </c>
       <c r="D16" s="0" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="E16" s="0">
-        <v>29.730863836131249</v>
+        <v>35.603895249624706</v>
       </c>
     </row>
     <row r="17">
@@ -408,16 +429,16 @@
         <v>1</v>
       </c>
       <c r="B17" s="0">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C17" s="0">
-        <v>0.92024047570868217</v>
+        <v>0.9081448328068078</v>
       </c>
       <c r="D17" s="0" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E17" s="0">
-        <v>6.1615970543571077</v>
+        <v>26.194327795228197</v>
       </c>
     </row>
     <row r="18">
@@ -425,16 +446,16 @@
         <v>1</v>
       </c>
       <c r="B18" s="0">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C18" s="0">
-        <v>0.92024047570868217</v>
+        <v>0.9081448328068078</v>
       </c>
       <c r="D18" s="0" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E18" s="0">
-        <v>5.2663774797050769</v>
+        <v>20.537565532314744</v>
       </c>
     </row>
     <row r="19">
@@ -442,16 +463,16 @@
         <v>1</v>
       </c>
       <c r="B19" s="0">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C19" s="0">
-        <v>0.92024047570868217</v>
+        <v>0.9081448328068078</v>
       </c>
       <c r="D19" s="0" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="E19" s="0">
-        <v>4.198691658461823</v>
+        <v>3.5762739188582162</v>
       </c>
     </row>
     <row r="20">
@@ -459,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="B20" s="0">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C20" s="0">
-        <v>0.92024047570868217</v>
+        <v>0.9081448328068078</v>
       </c>
       <c r="D20" s="0" t="s">
         <v>13</v>
       </c>
       <c r="E20" s="0">
-        <v>3.5226574825625945</v>
+        <v>3.3834986834684098</v>
       </c>
     </row>
     <row r="21">
@@ -476,16 +497,16 @@
         <v>1</v>
       </c>
       <c r="B21" s="0">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C21" s="0">
-        <v>0.92024047570868217</v>
+        <v>0.9081448328068078</v>
       </c>
       <c r="D21" s="0" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="E21" s="0">
-        <v>3.1127280060794602</v>
+        <v>2.0396995657108676</v>
       </c>
     </row>
     <row r="22">
@@ -493,16 +514,16 @@
         <v>1</v>
       </c>
       <c r="B22" s="0">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C22" s="0">
-        <v>0.94092848235749693</v>
+        <v>0.93740988155380123</v>
       </c>
       <c r="D22" s="0" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E22" s="0">
-        <v>134.57902262788485</v>
+        <v>100.54321833299335</v>
       </c>
     </row>
     <row r="23">
@@ -510,16 +531,16 @@
         <v>1</v>
       </c>
       <c r="B23" s="0">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C23" s="0">
-        <v>0.94092848235749693</v>
+        <v>0.93740988155380123</v>
       </c>
       <c r="D23" s="0" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E23" s="0">
-        <v>93.594849220691856</v>
+        <v>96.026025431403184</v>
       </c>
     </row>
     <row r="24">
@@ -527,16 +548,16 @@
         <v>1</v>
       </c>
       <c r="B24" s="0">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C24" s="0">
-        <v>0.94092848235749693</v>
+        <v>0.93740988155380123</v>
       </c>
       <c r="D24" s="0" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E24" s="0">
-        <v>86.673411104046735</v>
+        <v>76.1122191291701</v>
       </c>
     </row>
     <row r="25">
@@ -544,16 +565,16 @@
         <v>1</v>
       </c>
       <c r="B25" s="0">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C25" s="0">
-        <v>0.94092848235749693</v>
+        <v>0.93740988155380123</v>
       </c>
       <c r="D25" s="0" t="s">
         <v>9</v>
       </c>
       <c r="E25" s="0">
-        <v>73.718476220197545</v>
+        <v>56.006646252190059</v>
       </c>
     </row>
     <row r="26">
@@ -561,16 +582,16 @@
         <v>1</v>
       </c>
       <c r="B26" s="0">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C26" s="0">
-        <v>0.94092848235749693</v>
+        <v>0.93740988155380123</v>
       </c>
       <c r="D26" s="0" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="E26" s="0">
-        <v>39.153275054758886</v>
+        <v>26.807279270603875</v>
       </c>
     </row>
     <row r="27">
@@ -578,16 +599,16 @@
         <v>1</v>
       </c>
       <c r="B27" s="0">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C27" s="0">
-        <v>0.94092848235749693</v>
+        <v>0.93740988155380123</v>
       </c>
       <c r="D27" s="0" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="E27" s="0">
-        <v>7.8231151596070303</v>
+        <v>25.546293725827663</v>
       </c>
     </row>
     <row r="28">
@@ -595,16 +616,16 @@
         <v>1</v>
       </c>
       <c r="B28" s="0">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C28" s="0">
-        <v>0.94092848235749693</v>
+        <v>0.93740988155380123</v>
       </c>
       <c r="D28" s="0" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E28" s="0">
-        <v>6.0124587301483867</v>
+        <v>15.314942549192407</v>
       </c>
     </row>
     <row r="29">
@@ -612,16 +633,16 @@
         <v>1</v>
       </c>
       <c r="B29" s="0">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C29" s="0">
-        <v>0.94092848235749693</v>
+        <v>0.93740988155380123</v>
       </c>
       <c r="D29" s="0" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E29" s="0">
-        <v>5.3645863435377974</v>
+        <v>10.038097012212194</v>
       </c>
     </row>
     <row r="30">
@@ -629,16 +650,16 @@
         <v>1</v>
       </c>
       <c r="B30" s="0">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C30" s="0">
-        <v>0.94092848235749693</v>
+        <v>0.93740988155380123</v>
       </c>
       <c r="D30" s="0" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="E30" s="0">
-        <v>2.7838308352687648</v>
+        <v>2.5258520727691787</v>
       </c>
     </row>
     <row r="31">
@@ -646,16 +667,16 @@
         <v>1</v>
       </c>
       <c r="B31" s="0">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C31" s="0">
-        <v>0.94092848235749693</v>
+        <v>0.93740988155380123</v>
       </c>
       <c r="D31" s="0" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E31" s="0">
-        <v>2.7408941448779336</v>
+        <v>2.4743711981785941</v>
       </c>
     </row>
     <row r="32">
@@ -666,13 +687,13 @@
         <v>7</v>
       </c>
       <c r="C32" s="0">
-        <v>0.94007222886602781</v>
+        <v>0.90498560095903524</v>
       </c>
       <c r="D32" s="0" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E32" s="0">
-        <v>105.32350738169224</v>
+        <v>116.49986422230239</v>
       </c>
     </row>
     <row r="33">
@@ -683,13 +704,13 @@
         <v>7</v>
       </c>
       <c r="C33" s="0">
-        <v>0.94007222886602781</v>
+        <v>0.90498560095903524</v>
       </c>
       <c r="D33" s="0" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E33" s="0">
-        <v>95.064282972159447</v>
+        <v>101.96294839776517</v>
       </c>
     </row>
     <row r="34">
@@ -700,13 +721,13 @@
         <v>7</v>
       </c>
       <c r="C34" s="0">
-        <v>0.94007222886602781</v>
+        <v>0.90498560095903524</v>
       </c>
       <c r="D34" s="0" t="s">
         <v>7</v>
       </c>
       <c r="E34" s="0">
-        <v>94.317199602147014</v>
+        <v>89.827237827230107</v>
       </c>
     </row>
     <row r="35">
@@ -717,13 +738,13 @@
         <v>7</v>
       </c>
       <c r="C35" s="0">
-        <v>0.94007222886602781</v>
+        <v>0.90498560095903524</v>
       </c>
       <c r="D35" s="0" t="s">
         <v>9</v>
       </c>
       <c r="E35" s="0">
-        <v>73.600154842176266</v>
+        <v>59.202981765553744</v>
       </c>
     </row>
     <row r="36">
@@ -734,13 +755,13 @@
         <v>7</v>
       </c>
       <c r="C36" s="0">
-        <v>0.94007222886602781</v>
+        <v>0.90498560095903524</v>
       </c>
       <c r="D36" s="0" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="E36" s="0">
-        <v>28.144562469702901</v>
+        <v>51.986929909903203</v>
       </c>
     </row>
     <row r="37">
@@ -751,13 +772,13 @@
         <v>7</v>
       </c>
       <c r="C37" s="0">
-        <v>0.94007222886602781</v>
+        <v>0.90498560095903524</v>
       </c>
       <c r="D37" s="0" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E37" s="0">
-        <v>5.2174842219017457</v>
+        <v>21.493237271883753</v>
       </c>
     </row>
     <row r="38">
@@ -768,13 +789,13 @@
         <v>7</v>
       </c>
       <c r="C38" s="0">
-        <v>0.94007222886602781</v>
+        <v>0.90498560095903524</v>
       </c>
       <c r="D38" s="0" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E38" s="0">
-        <v>4.1143584603399717</v>
+        <v>20.801763782434495</v>
       </c>
     </row>
     <row r="39">
@@ -785,13 +806,13 @@
         <v>7</v>
       </c>
       <c r="C39" s="0">
-        <v>0.94007222886602781</v>
+        <v>0.90498560095903524</v>
       </c>
       <c r="D39" s="0" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E39" s="0">
-        <v>3.6809271079051147</v>
+        <v>4.9868857711057544</v>
       </c>
     </row>
     <row r="40">
@@ -802,13 +823,13 @@
         <v>7</v>
       </c>
       <c r="C40" s="0">
-        <v>0.94007222886602781</v>
+        <v>0.90498560095903524</v>
       </c>
       <c r="D40" s="0" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="E40" s="0">
-        <v>3.207487375159074</v>
+        <v>2.9114562609037087</v>
       </c>
     </row>
     <row r="41">
@@ -819,183 +840,183 @@
         <v>7</v>
       </c>
       <c r="C41" s="0">
-        <v>0.94007222886602781</v>
+        <v>0.90498560095903524</v>
       </c>
       <c r="D41" s="0" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E41" s="0">
-        <v>2.5896055172666799</v>
+        <v>2.7293181431362359</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="0" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B42" s="0">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C42" s="0">
-        <v>0.93047011369449439</v>
+        <v>0.90242614494408591</v>
       </c>
       <c r="D42" s="0" t="s">
         <v>8</v>
       </c>
       <c r="E42" s="0">
-        <v>6.8218373198248621</v>
+        <v>115.1289840470839</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="0" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B43" s="0">
+        <v>9</v>
+      </c>
+      <c r="C43" s="0">
+        <v>0.90242614494408591</v>
+      </c>
+      <c r="D43" s="0" t="s">
         <v>7</v>
       </c>
-      <c r="C43" s="0">
-        <v>0.93047011369449439</v>
-      </c>
-      <c r="D43" s="0" t="s">
-        <v>9</v>
-      </c>
       <c r="E43" s="0">
-        <v>1.3612782376054182</v>
+        <v>96.718688699973967</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="0" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B44" s="0">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C44" s="0">
-        <v>0.93047011369449439</v>
+        <v>0.90242614494408591</v>
       </c>
       <c r="D44" s="0" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E44" s="0">
-        <v>0.49054329336838598</v>
+        <v>85.550304784258898</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="0" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B45" s="0">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C45" s="0">
-        <v>0.93047011369449439</v>
+        <v>0.90242614494408591</v>
       </c>
       <c r="D45" s="0" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E45" s="0">
-        <v>0.34349735789040703</v>
+        <v>42.518895064016142</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="0" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B46" s="0">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C46" s="0">
-        <v>0.93047011369449439</v>
+        <v>0.90242614494408591</v>
       </c>
       <c r="D46" s="0" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E46" s="0">
-        <v>0.30912634330250482</v>
+        <v>38.500261638058269</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="0" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B47" s="0">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C47" s="0">
-        <v>0.93047011369449439</v>
+        <v>0.90242614494408591</v>
       </c>
       <c r="D47" s="0" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="E47" s="0">
-        <v>0.15242221907673159</v>
+        <v>31.61946598523086</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="0" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B48" s="0">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C48" s="0">
-        <v>0.93047011369449439</v>
+        <v>0.90242614494408591</v>
       </c>
       <c r="D48" s="0" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E48" s="0">
-        <v>0.12516357304986553</v>
+        <v>18.511811739765523</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="0" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B49" s="0">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C49" s="0">
-        <v>0.93047011369449439</v>
+        <v>0.90242614494408591</v>
       </c>
       <c r="D49" s="0" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="E49" s="0">
-        <v>0.080302234478879089</v>
+        <v>5.7559050677556014</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="0" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B50" s="0">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C50" s="0">
-        <v>0.93047011369449439</v>
+        <v>0.90242614494408591</v>
       </c>
       <c r="D50" s="0" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="E50" s="0">
-        <v>0.078172315228149991</v>
+        <v>2.3284440953992753</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="0" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B51" s="0">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C51" s="0">
-        <v>0.93047011369449439</v>
+        <v>0.90242614494408591</v>
       </c>
       <c r="D51" s="0" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="E51" s="0">
-        <v>0.046373750162676544</v>
+        <v>2.2087809887215886</v>
       </c>
     </row>
     <row r="52">
@@ -1003,16 +1024,16 @@
         <v>1</v>
       </c>
       <c r="B52" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C52" s="0">
-        <v>0.90938927214101328</v>
+        <v>0.90948710981266967</v>
       </c>
       <c r="D52" s="0" t="s">
         <v>8</v>
       </c>
       <c r="E52" s="0">
-        <v>155.11180196425391</v>
+        <v>129.25797255829718</v>
       </c>
     </row>
     <row r="53">
@@ -1020,16 +1041,16 @@
         <v>1</v>
       </c>
       <c r="B53" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C53" s="0">
-        <v>0.90938927214101328</v>
+        <v>0.90948710981266967</v>
       </c>
       <c r="D53" s="0" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E53" s="0">
-        <v>123.93611985773354</v>
+        <v>93.334235637445687</v>
       </c>
     </row>
     <row r="54">
@@ -1037,16 +1058,16 @@
         <v>1</v>
       </c>
       <c r="B54" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C54" s="0">
-        <v>0.90938927214101328</v>
+        <v>0.90948710981266967</v>
       </c>
       <c r="D54" s="0" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E54" s="0">
-        <v>81.226250185927469</v>
+        <v>74.198646291894505</v>
       </c>
     </row>
     <row r="55">
@@ -1054,16 +1075,16 @@
         <v>1</v>
       </c>
       <c r="B55" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C55" s="0">
-        <v>0.90938927214101328</v>
+        <v>0.90948710981266967</v>
       </c>
       <c r="D55" s="0" t="s">
         <v>9</v>
       </c>
       <c r="E55" s="0">
-        <v>72.719545216902844</v>
+        <v>51.375031790507677</v>
       </c>
     </row>
     <row r="56">
@@ -1071,16 +1092,16 @@
         <v>1</v>
       </c>
       <c r="B56" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C56" s="0">
-        <v>0.90938927214101328</v>
+        <v>0.90948710981266967</v>
       </c>
       <c r="D56" s="0" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="E56" s="0">
-        <v>25.892813510490569</v>
+        <v>25.335755856080212</v>
       </c>
     </row>
     <row r="57">
@@ -1088,16 +1109,16 @@
         <v>1</v>
       </c>
       <c r="B57" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C57" s="0">
-        <v>0.90938927214101328</v>
+        <v>0.90948710981266967</v>
       </c>
       <c r="D57" s="0" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="E57" s="0">
-        <v>6.4265608328078825</v>
+        <v>18.270514503331956</v>
       </c>
     </row>
     <row r="58">
@@ -1105,16 +1126,16 @@
         <v>1</v>
       </c>
       <c r="B58" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C58" s="0">
-        <v>0.90938927214101328</v>
+        <v>0.90948710981266967</v>
       </c>
       <c r="D58" s="0" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E58" s="0">
-        <v>5.0352157613289412</v>
+        <v>16.559326824696555</v>
       </c>
     </row>
     <row r="59">
@@ -1122,16 +1143,16 @@
         <v>1</v>
       </c>
       <c r="B59" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C59" s="0">
-        <v>0.90938927214101328</v>
+        <v>0.90948710981266967</v>
       </c>
       <c r="D59" s="0" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E59" s="0">
-        <v>4.5796106954214215</v>
+        <v>9.4719372012644527</v>
       </c>
     </row>
     <row r="60">
@@ -1139,16 +1160,16 @@
         <v>1</v>
       </c>
       <c r="B60" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C60" s="0">
-        <v>0.90938927214101328</v>
+        <v>0.90948710981266967</v>
       </c>
       <c r="D60" s="0" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E60" s="0">
-        <v>3.1485247422679885</v>
+        <v>2.8782301693384484</v>
       </c>
     </row>
     <row r="61">
@@ -1156,16 +1177,16 @@
         <v>1</v>
       </c>
       <c r="B61" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C61" s="0">
-        <v>0.90938927214101328</v>
+        <v>0.90948710981266967</v>
       </c>
       <c r="D61" s="0" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E61" s="0">
-        <v>3.0119028760801267</v>
+        <v>2.3532548111685943</v>
       </c>
     </row>
     <row r="62">
@@ -1173,16 +1194,16 @@
         <v>1</v>
       </c>
       <c r="B62" s="0">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C62" s="0">
-        <v>0.9039239956205527</v>
+        <v>0.93325786788245391</v>
       </c>
       <c r="D62" s="0" t="s">
         <v>8</v>
       </c>
       <c r="E62" s="0">
-        <v>129.90741835655118</v>
+        <v>104.05402018971994</v>
       </c>
     </row>
     <row r="63">
@@ -1190,16 +1211,16 @@
         <v>1</v>
       </c>
       <c r="B63" s="0">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C63" s="0">
-        <v>0.9039239956205527</v>
+        <v>0.93325786788245391</v>
       </c>
       <c r="D63" s="0" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E63" s="0">
-        <v>108.20216438546484</v>
+        <v>91.257220880734081</v>
       </c>
     </row>
     <row r="64">
@@ -1207,16 +1228,16 @@
         <v>1</v>
       </c>
       <c r="B64" s="0">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C64" s="0">
-        <v>0.9039239956205527</v>
+        <v>0.93325786788245391</v>
       </c>
       <c r="D64" s="0" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E64" s="0">
-        <v>99.966331412082724</v>
+        <v>80.182987076189889</v>
       </c>
     </row>
     <row r="65">
@@ -1224,16 +1245,16 @@
         <v>1</v>
       </c>
       <c r="B65" s="0">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C65" s="0">
-        <v>0.9039239956205527</v>
+        <v>0.93325786788245391</v>
       </c>
       <c r="D65" s="0" t="s">
         <v>9</v>
       </c>
       <c r="E65" s="0">
-        <v>73.368302651150955</v>
+        <v>61.9857765140653</v>
       </c>
     </row>
     <row r="66">
@@ -1241,16 +1262,16 @@
         <v>1</v>
       </c>
       <c r="B66" s="0">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C66" s="0">
-        <v>0.9039239956205527</v>
+        <v>0.93325786788245391</v>
       </c>
       <c r="D66" s="0" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="E66" s="0">
-        <v>29.313556031499594</v>
+        <v>23.310414628119883</v>
       </c>
     </row>
     <row r="67">
@@ -1258,16 +1279,16 @@
         <v>1</v>
       </c>
       <c r="B67" s="0">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C67" s="0">
-        <v>0.9039239956205527</v>
+        <v>0.93325786788245391</v>
       </c>
       <c r="D67" s="0" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="E67" s="0">
-        <v>4.395689002627762</v>
+        <v>21.761749432817592</v>
       </c>
     </row>
     <row r="68">
@@ -1275,16 +1296,16 @@
         <v>1</v>
       </c>
       <c r="B68" s="0">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C68" s="0">
-        <v>0.9039239956205527</v>
+        <v>0.93325786788245391</v>
       </c>
       <c r="D68" s="0" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="E68" s="0">
-        <v>3.5744187410989063</v>
+        <v>13.372210294482141</v>
       </c>
     </row>
     <row r="69">
@@ -1292,16 +1313,16 @@
         <v>1</v>
       </c>
       <c r="B69" s="0">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C69" s="0">
-        <v>0.9039239956205527</v>
+        <v>0.93325786788245391</v>
       </c>
       <c r="D69" s="0" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E69" s="0">
-        <v>3.3205496654055908</v>
+        <v>8.2713039722634178</v>
       </c>
     </row>
     <row r="70">
@@ -1309,16 +1330,16 @@
         <v>1</v>
       </c>
       <c r="B70" s="0">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C70" s="0">
-        <v>0.9039239956205527</v>
+        <v>0.93325786788245391</v>
       </c>
       <c r="D70" s="0" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="E70" s="0">
-        <v>3.0406475098793995</v>
+        <v>2.5269665002060449</v>
       </c>
     </row>
     <row r="71">
@@ -1326,16 +1347,16 @@
         <v>1</v>
       </c>
       <c r="B71" s="0">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C71" s="0">
-        <v>0.9039239956205527</v>
+        <v>0.93325786788245391</v>
       </c>
       <c r="D71" s="0" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E71" s="0">
-        <v>2.9290885465476122</v>
+        <v>1.8996823380945909</v>
       </c>
     </row>
     <row r="72">
@@ -1346,13 +1367,13 @@
         <v>12</v>
       </c>
       <c r="C72" s="0">
-        <v>0.91531618293363248</v>
+        <v>0.90148022793098193</v>
       </c>
       <c r="D72" s="0" t="s">
         <v>8</v>
       </c>
       <c r="E72" s="0">
-        <v>164.36253991410297</v>
+        <v>132.74345785331596</v>
       </c>
     </row>
     <row r="73">
@@ -1363,13 +1384,13 @@
         <v>12</v>
       </c>
       <c r="C73" s="0">
-        <v>0.91531618293363248</v>
+        <v>0.90148022793098193</v>
       </c>
       <c r="D73" s="0" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E73" s="0">
-        <v>108.59092144197977</v>
+        <v>87.098411412337143</v>
       </c>
     </row>
     <row r="74">
@@ -1380,13 +1401,13 @@
         <v>12</v>
       </c>
       <c r="C74" s="0">
-        <v>0.91531618293363248</v>
+        <v>0.90148022793098193</v>
       </c>
       <c r="D74" s="0" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E74" s="0">
-        <v>102.96459019025316</v>
+        <v>72.102735046908037</v>
       </c>
     </row>
     <row r="75">
@@ -1397,13 +1418,13 @@
         <v>12</v>
       </c>
       <c r="C75" s="0">
-        <v>0.91531618293363248</v>
+        <v>0.90148022793098193</v>
       </c>
       <c r="D75" s="0" t="s">
         <v>9</v>
       </c>
       <c r="E75" s="0">
-        <v>76.318542095378021</v>
+        <v>63.766503058117017</v>
       </c>
     </row>
     <row r="76">
@@ -1414,13 +1435,13 @@
         <v>12</v>
       </c>
       <c r="C76" s="0">
-        <v>0.91531618293363248</v>
+        <v>0.90148022793098193</v>
       </c>
       <c r="D76" s="0" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="E76" s="0">
-        <v>28.681946571674974</v>
+        <v>37.282246034741</v>
       </c>
     </row>
     <row r="77">
@@ -1431,13 +1452,13 @@
         <v>12</v>
       </c>
       <c r="C77" s="0">
-        <v>0.91531618293363248</v>
+        <v>0.90148022793098193</v>
       </c>
       <c r="D77" s="0" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E77" s="0">
-        <v>7.3649171221165348</v>
+        <v>31.672984426524003</v>
       </c>
     </row>
     <row r="78">
@@ -1448,13 +1469,13 @@
         <v>12</v>
       </c>
       <c r="C78" s="0">
-        <v>0.91531618293363248</v>
+        <v>0.90148022793098193</v>
       </c>
       <c r="D78" s="0" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E78" s="0">
-        <v>4.2997007072429181</v>
+        <v>18.123349095883558</v>
       </c>
     </row>
     <row r="79">
@@ -1465,13 +1486,13 @@
         <v>12</v>
       </c>
       <c r="C79" s="0">
-        <v>0.91531618293363248</v>
+        <v>0.90148022793098193</v>
       </c>
       <c r="D79" s="0" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="E79" s="0">
-        <v>3.665022803670142</v>
+        <v>5.4577310847567766</v>
       </c>
     </row>
     <row r="80">
@@ -1482,13 +1503,13 @@
         <v>12</v>
       </c>
       <c r="C80" s="0">
-        <v>0.91531618293363248</v>
+        <v>0.90148022793098193</v>
       </c>
       <c r="D80" s="0" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E80" s="0">
-        <v>3.2138215242600796</v>
+        <v>1.8068954617667417</v>
       </c>
     </row>
     <row r="81">
@@ -1499,13 +1520,13 @@
         <v>12</v>
       </c>
       <c r="C81" s="0">
-        <v>0.91531618293363248</v>
+        <v>0.90148022793098193</v>
       </c>
       <c r="D81" s="0" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="E81" s="0">
-        <v>3.0697406255491448</v>
+        <v>1.6059730307290707</v>
       </c>
     </row>
     <row r="82">
@@ -1516,13 +1537,13 @@
         <v>13</v>
       </c>
       <c r="C82" s="0">
-        <v>0.92563221427200115</v>
+        <v>0.91510568470563136</v>
       </c>
       <c r="D82" s="0" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E82" s="0">
-        <v>122.6759111021405</v>
+        <v>105.89724217216234</v>
       </c>
     </row>
     <row r="83">
@@ -1533,13 +1554,13 @@
         <v>13</v>
       </c>
       <c r="C83" s="0">
-        <v>0.92563221427200115</v>
+        <v>0.91510568470563136</v>
       </c>
       <c r="D83" s="0" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E83" s="0">
-        <v>106.40729782581428</v>
+        <v>98.536847716071591</v>
       </c>
     </row>
     <row r="84">
@@ -1550,13 +1571,13 @@
         <v>13</v>
       </c>
       <c r="C84" s="0">
-        <v>0.92563221427200115</v>
+        <v>0.91510568470563136</v>
       </c>
       <c r="D84" s="0" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E84" s="0">
-        <v>99.354766512436441</v>
+        <v>95.348721520007985</v>
       </c>
     </row>
     <row r="85">
@@ -1567,13 +1588,13 @@
         <v>13</v>
       </c>
       <c r="C85" s="0">
-        <v>0.92563221427200115</v>
+        <v>0.91510568470563136</v>
       </c>
       <c r="D85" s="0" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="E85" s="0">
-        <v>93.457702719862041</v>
+        <v>63.72985431282558</v>
       </c>
     </row>
     <row r="86">
@@ -1584,13 +1605,13 @@
         <v>13</v>
       </c>
       <c r="C86" s="0">
-        <v>0.92563221427200115</v>
+        <v>0.91510568470563136</v>
       </c>
       <c r="D86" s="0" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E86" s="0">
-        <v>38.460612792533503</v>
+        <v>42.654294743658212</v>
       </c>
     </row>
     <row r="87">
@@ -1601,13 +1622,13 @@
         <v>13</v>
       </c>
       <c r="C87" s="0">
-        <v>0.92563221427200115</v>
+        <v>0.91510568470563136</v>
       </c>
       <c r="D87" s="0" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E87" s="0">
-        <v>6.8615384672138182</v>
+        <v>16.666558076847885</v>
       </c>
     </row>
     <row r="88">
@@ -1618,13 +1639,13 @@
         <v>13</v>
       </c>
       <c r="C88" s="0">
-        <v>0.92563221427200115</v>
+        <v>0.91510568470563136</v>
       </c>
       <c r="D88" s="0" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E88" s="0">
-        <v>3.7710758408491194</v>
+        <v>13.312040798369422</v>
       </c>
     </row>
     <row r="89">
@@ -1635,13 +1656,13 @@
         <v>13</v>
       </c>
       <c r="C89" s="0">
-        <v>0.92563221427200115</v>
+        <v>0.91510568470563136</v>
       </c>
       <c r="D89" s="0" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E89" s="0">
-        <v>3.6225433756210923</v>
+        <v>9.7316802695138165</v>
       </c>
     </row>
     <row r="90">
@@ -1652,13 +1673,13 @@
         <v>13</v>
       </c>
       <c r="C90" s="0">
-        <v>0.92563221427200115</v>
+        <v>0.91510568470563136</v>
       </c>
       <c r="D90" s="0" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E90" s="0">
-        <v>2.9426027493139788</v>
+        <v>3.9500266794088916</v>
       </c>
     </row>
     <row r="91">
@@ -1669,13 +1690,13 @@
         <v>13</v>
       </c>
       <c r="C91" s="0">
-        <v>0.92563221427200115</v>
+        <v>0.91510568470563136</v>
       </c>
       <c r="D91" s="0" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="E91" s="0">
-        <v>2.8997047669143456</v>
+        <v>2.0602854962269253</v>
       </c>
     </row>
     <row r="92">
@@ -1686,13 +1707,13 @@
         <v>15</v>
       </c>
       <c r="C92" s="0">
-        <v>0.92616216708584032</v>
+        <v>0.93093305170300833</v>
       </c>
       <c r="D92" s="0" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E92" s="0">
-        <v>148.83424664783848</v>
+        <v>147.1536986227448</v>
       </c>
     </row>
     <row r="93">
@@ -1703,13 +1724,13 @@
         <v>15</v>
       </c>
       <c r="C93" s="0">
-        <v>0.92616216708584032</v>
+        <v>0.93093305170300833</v>
       </c>
       <c r="D93" s="0" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E93" s="0">
-        <v>132.36959891177219</v>
+        <v>109.11341657334788</v>
       </c>
     </row>
     <row r="94">
@@ -1720,13 +1741,13 @@
         <v>15</v>
       </c>
       <c r="C94" s="0">
-        <v>0.92616216708584032</v>
+        <v>0.93093305170300833</v>
       </c>
       <c r="D94" s="0" t="s">
         <v>7</v>
       </c>
       <c r="E94" s="0">
-        <v>84.492870975633053</v>
+        <v>79.772250345238731</v>
       </c>
     </row>
     <row r="95">
@@ -1737,13 +1758,13 @@
         <v>15</v>
       </c>
       <c r="C95" s="0">
-        <v>0.92616216708584032</v>
+        <v>0.93093305170300833</v>
       </c>
       <c r="D95" s="0" t="s">
         <v>9</v>
       </c>
       <c r="E95" s="0">
-        <v>70.567575798628738</v>
+        <v>48.529284022013513</v>
       </c>
     </row>
     <row r="96">
@@ -1754,13 +1775,13 @@
         <v>15</v>
       </c>
       <c r="C96" s="0">
-        <v>0.92616216708584032</v>
+        <v>0.93093305170300833</v>
       </c>
       <c r="D96" s="0" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="E96" s="0">
-        <v>25.3044448164381</v>
+        <v>31.745669983895581</v>
       </c>
     </row>
     <row r="97">
@@ -1771,13 +1792,13 @@
         <v>15</v>
       </c>
       <c r="C97" s="0">
-        <v>0.92616216708584032</v>
+        <v>0.93093305170300833</v>
       </c>
       <c r="D97" s="0" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="E97" s="0">
-        <v>5.1107346159144518</v>
+        <v>19.044619085338606</v>
       </c>
     </row>
     <row r="98">
@@ -1788,13 +1809,13 @@
         <v>15</v>
       </c>
       <c r="C98" s="0">
-        <v>0.92616216708584032</v>
+        <v>0.93093305170300833</v>
       </c>
       <c r="D98" s="0" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E98" s="0">
-        <v>3.6450513215037934</v>
+        <v>14.404808161391967</v>
       </c>
     </row>
     <row r="99">
@@ -1805,13 +1826,13 @@
         <v>15</v>
       </c>
       <c r="C99" s="0">
-        <v>0.92616216708584032</v>
+        <v>0.93093305170300833</v>
       </c>
       <c r="D99" s="0" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="E99" s="0">
-        <v>3.2659425701416591</v>
+        <v>12.819982296915967</v>
       </c>
     </row>
     <row r="100">
@@ -1822,13 +1843,13 @@
         <v>15</v>
       </c>
       <c r="C100" s="0">
-        <v>0.92616216708584032</v>
+        <v>0.93093305170300833</v>
       </c>
       <c r="D100" s="0" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="E100" s="0">
-        <v>2.9981133193112037</v>
+        <v>2.642872478252174</v>
       </c>
     </row>
     <row r="101">
@@ -1839,13 +1860,13 @@
         <v>15</v>
       </c>
       <c r="C101" s="0">
-        <v>0.92616216708584032</v>
+        <v>0.93093305170300833</v>
       </c>
       <c r="D101" s="0" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E101" s="0">
-        <v>2.5415649956623323</v>
+        <v>2.2869559043420136</v>
       </c>
     </row>
     <row r="102">
@@ -1856,13 +1877,13 @@
         <v>16</v>
       </c>
       <c r="C102" s="0">
-        <v>0.91583279044951871</v>
+        <v>0.95143101782472606</v>
       </c>
       <c r="D102" s="0" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E102" s="0">
-        <v>135.27227859029449</v>
+        <v>106.49734526414197</v>
       </c>
     </row>
     <row r="103">
@@ -1873,13 +1894,13 @@
         <v>16</v>
       </c>
       <c r="C103" s="0">
-        <v>0.91583279044951871</v>
+        <v>0.95143101782472606</v>
       </c>
       <c r="D103" s="0" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E103" s="0">
-        <v>121.32770516590298</v>
+        <v>96.339498844012269</v>
       </c>
     </row>
     <row r="104">
@@ -1890,13 +1911,13 @@
         <v>16</v>
       </c>
       <c r="C104" s="0">
-        <v>0.91583279044951871</v>
+        <v>0.95143101782472606</v>
       </c>
       <c r="D104" s="0" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E104" s="0">
-        <v>112.84748427458713</v>
+        <v>75.893194635173188</v>
       </c>
     </row>
     <row r="105">
@@ -1907,13 +1928,13 @@
         <v>16</v>
       </c>
       <c r="C105" s="0">
-        <v>0.91583279044951871</v>
+        <v>0.95143101782472606</v>
       </c>
       <c r="D105" s="0" t="s">
         <v>9</v>
       </c>
       <c r="E105" s="0">
-        <v>69.039842274862878</v>
+        <v>44.88818527439782</v>
       </c>
     </row>
     <row r="106">
@@ -1924,13 +1945,13 @@
         <v>16</v>
       </c>
       <c r="C106" s="0">
-        <v>0.91583279044951871</v>
+        <v>0.95143101782472606</v>
       </c>
       <c r="D106" s="0" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="E106" s="0">
-        <v>24.877398223028745</v>
+        <v>18.141564518325325</v>
       </c>
     </row>
     <row r="107">
@@ -1941,13 +1962,13 @@
         <v>16</v>
       </c>
       <c r="C107" s="0">
-        <v>0.91583279044951871</v>
+        <v>0.95143101782472606</v>
       </c>
       <c r="D107" s="0" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E107" s="0">
-        <v>3.7354401761116458</v>
+        <v>15.368647210784649</v>
       </c>
     </row>
     <row r="108">
@@ -1958,13 +1979,13 @@
         <v>16</v>
       </c>
       <c r="C108" s="0">
-        <v>0.91583279044951871</v>
+        <v>0.95143101782472606</v>
       </c>
       <c r="D108" s="0" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="E108" s="0">
-        <v>3.4274014230470193</v>
+        <v>13.424672257244419</v>
       </c>
     </row>
     <row r="109">
@@ -1975,13 +1996,13 @@
         <v>16</v>
       </c>
       <c r="C109" s="0">
-        <v>0.91583279044951871</v>
+        <v>0.95143101782472606</v>
       </c>
       <c r="D109" s="0" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="E109" s="0">
-        <v>3.2598154658846301</v>
+        <v>11.315912283160328</v>
       </c>
     </row>
     <row r="110">
@@ -1992,13 +2013,13 @@
         <v>16</v>
       </c>
       <c r="C110" s="0">
-        <v>0.91583279044951871</v>
+        <v>0.95143101782472606</v>
       </c>
       <c r="D110" s="0" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E110" s="0">
-        <v>2.7792439106022733</v>
+        <v>2.8193682872310588</v>
       </c>
     </row>
     <row r="111">
@@ -2009,353 +2030,353 @@
         <v>16</v>
       </c>
       <c r="C111" s="0">
-        <v>0.91583279044951871</v>
+        <v>0.95143101782472606</v>
       </c>
       <c r="D111" s="0" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E111" s="0">
-        <v>2.5447514378549703</v>
+        <v>2.1941531147766637</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="0" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B112" s="0">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C112" s="0">
-        <v>0.94012240789535007</v>
+        <v>0.91674544222119358</v>
       </c>
       <c r="D112" s="0" t="s">
         <v>8</v>
       </c>
       <c r="E112" s="0">
-        <v>141.1315846408026</v>
+        <v>6.0556819142702834</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="0" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B113" s="0">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C113" s="0">
-        <v>0.94012240789535007</v>
+        <v>0.91674544222119358</v>
       </c>
       <c r="D113" s="0" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E113" s="0">
-        <v>98.920969760422324</v>
+        <v>1.4573403304889623</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="0" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B114" s="0">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C114" s="0">
-        <v>0.94012240789535007</v>
+        <v>0.91674544222119358</v>
       </c>
       <c r="D114" s="0" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E114" s="0">
-        <v>82.185271966791703</v>
+        <v>0.96879168475582222</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="0" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B115" s="0">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C115" s="0">
-        <v>0.94012240789535007</v>
+        <v>0.91674544222119358</v>
       </c>
       <c r="D115" s="0" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E115" s="0">
-        <v>62.202124277784769</v>
+        <v>0.16833037090418709</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="0" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B116" s="0">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C116" s="0">
-        <v>0.94012240789535007</v>
+        <v>0.91674544222119358</v>
       </c>
       <c r="D116" s="0" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="E116" s="0">
-        <v>30.68103369442219</v>
+        <v>0.10474323185824351</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="0" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B117" s="0">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C117" s="0">
-        <v>0.94012240789535007</v>
+        <v>0.91674544222119358</v>
       </c>
       <c r="D117" s="0" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="E117" s="0">
-        <v>4.0171580633881554</v>
+        <v>0.0687840356347829</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="0" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B118" s="0">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C118" s="0">
-        <v>0.94012240789535007</v>
+        <v>0.91674544222119358</v>
       </c>
       <c r="D118" s="0" t="s">
         <v>16</v>
       </c>
       <c r="E118" s="0">
-        <v>4.0050574409545376</v>
+        <v>0.048756022453830046</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="0" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B119" s="0">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C119" s="0">
-        <v>0.94012240789535007</v>
+        <v>0.91674544222119358</v>
       </c>
       <c r="D119" s="0" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="E119" s="0">
-        <v>3.8684780456674384</v>
+        <v>0.047904148205655611</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="0" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B120" s="0">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C120" s="0">
-        <v>0.94012240789535007</v>
+        <v>0.91674544222119358</v>
       </c>
       <c r="D120" s="0" t="s">
         <v>18</v>
       </c>
       <c r="E120" s="0">
-        <v>2.808260395730573</v>
+        <v>0.039044287980524041</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="0" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B121" s="0">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C121" s="0">
-        <v>0.94012240789535007</v>
+        <v>0.91674544222119358</v>
       </c>
       <c r="D121" s="0" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E121" s="0">
-        <v>2.2100961740726599</v>
+        <v>0.037731706640305965</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="0" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B122" s="0">
         <v>17</v>
       </c>
       <c r="C122" s="0">
-        <v>0.90935062038771663</v>
+        <v>0.93095875248273052</v>
       </c>
       <c r="D122" s="0" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E122" s="0">
-        <v>6.9157402947731876</v>
+        <v>118.85508526908916</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="0" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B123" s="0">
         <v>17</v>
       </c>
       <c r="C123" s="0">
-        <v>0.90935062038771663</v>
+        <v>0.93095875248273052</v>
       </c>
       <c r="D123" s="0" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E123" s="0">
-        <v>1.744774718543364</v>
+        <v>108.98836068809189</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="0" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B124" s="0">
         <v>17</v>
       </c>
       <c r="C124" s="0">
-        <v>0.90935062038771663</v>
+        <v>0.93095875248273052</v>
       </c>
       <c r="D124" s="0" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E124" s="0">
-        <v>0.8948385463439622</v>
+        <v>96.73985205592389</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="0" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B125" s="0">
         <v>17</v>
       </c>
       <c r="C125" s="0">
-        <v>0.90935062038771663</v>
+        <v>0.93095875248273052</v>
       </c>
       <c r="D125" s="0" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E125" s="0">
-        <v>0.21191701942587524</v>
+        <v>63.008690890743722</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="0" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B126" s="0">
         <v>17</v>
       </c>
       <c r="C126" s="0">
-        <v>0.90935062038771663</v>
+        <v>0.93095875248273052</v>
       </c>
       <c r="D126" s="0" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="E126" s="0">
-        <v>0.10598486664866912</v>
+        <v>30.83909829334398</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="0" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B127" s="0">
         <v>17</v>
       </c>
       <c r="C127" s="0">
-        <v>0.90935062038771663</v>
+        <v>0.93095875248273052</v>
       </c>
       <c r="D127" s="0" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E127" s="0">
-        <v>0.096598805110677782</v>
+        <v>23.841382563431054</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="0" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B128" s="0">
         <v>17</v>
       </c>
       <c r="C128" s="0">
-        <v>0.90935062038771663</v>
+        <v>0.93095875248273052</v>
       </c>
       <c r="D128" s="0" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="E128" s="0">
-        <v>0.063669650420625765</v>
+        <v>19.169616237887361</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="0" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B129" s="0">
         <v>17</v>
       </c>
       <c r="C129" s="0">
-        <v>0.90935062038771663</v>
+        <v>0.93095875248273052</v>
       </c>
       <c r="D129" s="0" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="E129" s="0">
-        <v>0.052370882560472641</v>
+        <v>7.2043411445734709</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="0" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B130" s="0">
         <v>17</v>
       </c>
       <c r="C130" s="0">
-        <v>0.90935062038771663</v>
+        <v>0.93095875248273052</v>
       </c>
       <c r="D130" s="0" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E130" s="0">
-        <v>0.052008302913103405</v>
+        <v>3.4881830178517377</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="0" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B131" s="0">
         <v>17</v>
       </c>
       <c r="C131" s="0">
-        <v>0.90935062038771663</v>
+        <v>0.93095875248273052</v>
       </c>
       <c r="D131" s="0" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="E131" s="0">
-        <v>0.031195789575382694</v>
+        <v>2.2380499442611081</v>
       </c>
     </row>
     <row r="132">
@@ -2366,13 +2387,13 @@
         <v>18</v>
       </c>
       <c r="C132" s="0">
-        <v>0.9370021350085258</v>
+        <v>0.9102851145021631</v>
       </c>
       <c r="D132" s="0" t="s">
         <v>8</v>
       </c>
       <c r="E132" s="0">
-        <v>130.96660569851312</v>
+        <v>117.98109877197045</v>
       </c>
     </row>
     <row r="133">
@@ -2383,13 +2404,13 @@
         <v>18</v>
       </c>
       <c r="C133" s="0">
-        <v>0.9370021350085258</v>
+        <v>0.9102851145021631</v>
       </c>
       <c r="D133" s="0" t="s">
         <v>7</v>
       </c>
       <c r="E133" s="0">
-        <v>92.969395010874166</v>
+        <v>84.320436695935626</v>
       </c>
     </row>
     <row r="134">
@@ -2400,13 +2421,13 @@
         <v>18</v>
       </c>
       <c r="C134" s="0">
-        <v>0.9370021350085258</v>
+        <v>0.9102851145021631</v>
       </c>
       <c r="D134" s="0" t="s">
         <v>6</v>
       </c>
       <c r="E134" s="0">
-        <v>90.572487993989</v>
+        <v>79.613515362310679</v>
       </c>
     </row>
     <row r="135">
@@ -2417,13 +2438,13 @@
         <v>18</v>
       </c>
       <c r="C135" s="0">
-        <v>0.9370021350085258</v>
+        <v>0.9102851145021631</v>
       </c>
       <c r="D135" s="0" t="s">
         <v>9</v>
       </c>
       <c r="E135" s="0">
-        <v>73.474152382326224</v>
+        <v>50.292643425902753</v>
       </c>
     </row>
     <row r="136">
@@ -2434,13 +2455,13 @@
         <v>18</v>
       </c>
       <c r="C136" s="0">
-        <v>0.9370021350085258</v>
+        <v>0.9102851145021631</v>
       </c>
       <c r="D136" s="0" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="E136" s="0">
-        <v>28.883422387289002</v>
+        <v>35.21709345038559</v>
       </c>
     </row>
     <row r="137">
@@ -2451,13 +2472,13 @@
         <v>18</v>
       </c>
       <c r="C137" s="0">
-        <v>0.9370021350085258</v>
+        <v>0.9102851145021631</v>
       </c>
       <c r="D137" s="0" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E137" s="0">
-        <v>3.7855315740897955</v>
+        <v>20.104690547886921</v>
       </c>
     </row>
     <row r="138">
@@ -2468,13 +2489,13 @@
         <v>18</v>
       </c>
       <c r="C138" s="0">
-        <v>0.9370021350085258</v>
+        <v>0.9102851145021631</v>
       </c>
       <c r="D138" s="0" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E138" s="0">
-        <v>3.1917151712187124</v>
+        <v>16.530636246039208</v>
       </c>
     </row>
     <row r="139">
@@ -2485,13 +2506,13 @@
         <v>18</v>
       </c>
       <c r="C139" s="0">
-        <v>0.9370021350085258</v>
+        <v>0.9102851145021631</v>
       </c>
       <c r="D139" s="0" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E139" s="0">
-        <v>3.1807175039220645</v>
+        <v>4.6656485786375566</v>
       </c>
     </row>
     <row r="140">
@@ -2502,13 +2523,13 @@
         <v>18</v>
       </c>
       <c r="C140" s="0">
-        <v>0.9370021350085258</v>
+        <v>0.9102851145021631</v>
       </c>
       <c r="D140" s="0" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E140" s="0">
-        <v>2.8912963589942859</v>
+        <v>2.9696208884089672</v>
       </c>
     </row>
     <row r="141">
@@ -2519,183 +2540,183 @@
         <v>18</v>
       </c>
       <c r="C141" s="0">
-        <v>0.9370021350085258</v>
+        <v>0.9102851145021631</v>
       </c>
       <c r="D141" s="0" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E141" s="0">
-        <v>2.5498058813373006</v>
+        <v>2.3500965511351857</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="0" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B142" s="0">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C142" s="0">
-        <v>0.91059723921610203</v>
+        <v>0.91210135361672096</v>
       </c>
       <c r="D142" s="0" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E142" s="0">
-        <v>116.77423119234817</v>
+        <v>7.0511234655620276</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="0" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B143" s="0">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C143" s="0">
-        <v>0.91059723921610203</v>
+        <v>0.91210135361672096</v>
       </c>
       <c r="D143" s="0" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E143" s="0">
-        <v>115.95361053058812</v>
+        <v>1.5459110870590291</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="0" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B144" s="0">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C144" s="0">
-        <v>0.91059723921610203</v>
+        <v>0.91210135361672096</v>
       </c>
       <c r="D144" s="0" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E144" s="0">
-        <v>109.90839798257853</v>
+        <v>0.49032524536968741</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="0" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B145" s="0">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C145" s="0">
-        <v>0.91059723921610203</v>
+        <v>0.91210135361672096</v>
       </c>
       <c r="D145" s="0" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E145" s="0">
-        <v>82.78179096235877</v>
+        <v>0.182177598285893</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="0" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B146" s="0">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C146" s="0">
-        <v>0.91059723921610203</v>
+        <v>0.91210135361672096</v>
       </c>
       <c r="D146" s="0" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="E146" s="0">
-        <v>38.869919074331847</v>
+        <v>0.095060386760481438</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="0" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B147" s="0">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C147" s="0">
-        <v>0.91059723921610203</v>
+        <v>0.91210135361672096</v>
       </c>
       <c r="D147" s="0" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="E147" s="0">
-        <v>5.2406241464380097</v>
+        <v>0.094974452071677845</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="0" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B148" s="0">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C148" s="0">
-        <v>0.91059723921610203</v>
+        <v>0.91210135361672096</v>
       </c>
       <c r="D148" s="0" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E148" s="0">
-        <v>4.5546114872153183</v>
+        <v>0.086182308579718689</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="0" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B149" s="0">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C149" s="0">
-        <v>0.91059723921610203</v>
+        <v>0.91210135361672096</v>
       </c>
       <c r="D149" s="0" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="E149" s="0">
-        <v>4.4330413944178666</v>
+        <v>0.068547890624141725</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="0" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B150" s="0">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C150" s="0">
-        <v>0.91059723921610203</v>
+        <v>0.91210135361672096</v>
       </c>
       <c r="D150" s="0" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="E150" s="0">
-        <v>3.7617676860384619</v>
+        <v>0.061480029831217323</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="0" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B151" s="0">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C151" s="0">
-        <v>0.91059723921610203</v>
+        <v>0.91210135361672096</v>
       </c>
       <c r="D151" s="0" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E151" s="0">
-        <v>3.406521583461652</v>
+        <v>0.057903813138154563</v>
       </c>
     </row>
     <row r="152">
@@ -2706,13 +2727,13 @@
         <v>20</v>
       </c>
       <c r="C152" s="0">
-        <v>0.92420781281826114</v>
+        <v>0.93791145455655889</v>
       </c>
       <c r="D152" s="0" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E152" s="0">
-        <v>110.0101445735513</v>
+        <v>116.54440618285467</v>
       </c>
     </row>
     <row r="153">
@@ -2723,13 +2744,13 @@
         <v>20</v>
       </c>
       <c r="C153" s="0">
-        <v>0.92420781281826114</v>
+        <v>0.93791145455655889</v>
       </c>
       <c r="D153" s="0" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E153" s="0">
-        <v>106.76399952432405</v>
+        <v>112.82944395595614</v>
       </c>
     </row>
     <row r="154">
@@ -2740,13 +2761,13 @@
         <v>20</v>
       </c>
       <c r="C154" s="0">
-        <v>0.92420781281826114</v>
+        <v>0.93791145455655889</v>
       </c>
       <c r="D154" s="0" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E154" s="0">
-        <v>98.423882642702836</v>
+        <v>76.103373706063209</v>
       </c>
     </row>
     <row r="155">
@@ -2757,13 +2778,13 @@
         <v>20</v>
       </c>
       <c r="C155" s="0">
-        <v>0.92420781281826114</v>
+        <v>0.93791145455655889</v>
       </c>
       <c r="D155" s="0" t="s">
         <v>9</v>
       </c>
       <c r="E155" s="0">
-        <v>81.152396370346736</v>
+        <v>63.613015963867582</v>
       </c>
     </row>
     <row r="156">
@@ -2774,13 +2795,13 @@
         <v>20</v>
       </c>
       <c r="C156" s="0">
-        <v>0.92420781281826114</v>
+        <v>0.93791145455655889</v>
       </c>
       <c r="D156" s="0" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="E156" s="0">
-        <v>34.42556490506113</v>
+        <v>33.097658490845582</v>
       </c>
     </row>
     <row r="157">
@@ -2791,13 +2812,13 @@
         <v>20</v>
       </c>
       <c r="C157" s="0">
-        <v>0.92420781281826114</v>
+        <v>0.93791145455655889</v>
       </c>
       <c r="D157" s="0" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="E157" s="0">
-        <v>4.0768826341751216</v>
+        <v>15.643989028632994</v>
       </c>
     </row>
     <row r="158">
@@ -2808,13 +2829,13 @@
         <v>20</v>
       </c>
       <c r="C158" s="0">
-        <v>0.92420781281826114</v>
+        <v>0.93791145455655889</v>
       </c>
       <c r="D158" s="0" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E158" s="0">
-        <v>3.6631875955752093</v>
+        <v>14.076440798551527</v>
       </c>
     </row>
     <row r="159">
@@ -2825,13 +2846,13 @@
         <v>20</v>
       </c>
       <c r="C159" s="0">
-        <v>0.92420781281826114</v>
+        <v>0.93791145455655889</v>
       </c>
       <c r="D159" s="0" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="E159" s="0">
-        <v>3.5440463278519836</v>
+        <v>6.0785653929330303</v>
       </c>
     </row>
     <row r="160">
@@ -2842,13 +2863,13 @@
         <v>20</v>
       </c>
       <c r="C160" s="0">
-        <v>0.92420781281826114</v>
+        <v>0.93791145455655889</v>
       </c>
       <c r="D160" s="0" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="E160" s="0">
-        <v>3.3059140694572271</v>
+        <v>2.3708870611461617</v>
       </c>
     </row>
     <row r="161">
@@ -2859,13 +2880,13 @@
         <v>20</v>
       </c>
       <c r="C161" s="0">
-        <v>0.92420781281826114</v>
+        <v>0.93791145455655889</v>
       </c>
       <c r="D161" s="0" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E161" s="0">
-        <v>2.9877710505789956</v>
+        <v>1.9841260286180074</v>
       </c>
     </row>
     <row r="162">
@@ -2873,16 +2894,16 @@
         <v>1</v>
       </c>
       <c r="B162" s="0">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C162" s="0">
-        <v>0.93156588062566326</v>
+        <v>0.91030297567518581</v>
       </c>
       <c r="D162" s="0" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E162" s="0">
-        <v>114.72659402724166</v>
+        <v>125.82682901150834</v>
       </c>
     </row>
     <row r="163">
@@ -2890,16 +2911,16 @@
         <v>1</v>
       </c>
       <c r="B163" s="0">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C163" s="0">
-        <v>0.93156588062566326</v>
+        <v>0.91030297567518581</v>
       </c>
       <c r="D163" s="0" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E163" s="0">
-        <v>113.88187341991288</v>
+        <v>105.30773159141405</v>
       </c>
     </row>
     <row r="164">
@@ -2907,16 +2928,16 @@
         <v>1</v>
       </c>
       <c r="B164" s="0">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C164" s="0">
-        <v>0.93156588062566326</v>
+        <v>0.91030297567518581</v>
       </c>
       <c r="D164" s="0" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E164" s="0">
-        <v>100.60455684949765</v>
+        <v>101.25343966483442</v>
       </c>
     </row>
     <row r="165">
@@ -2924,16 +2945,16 @@
         <v>1</v>
       </c>
       <c r="B165" s="0">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C165" s="0">
-        <v>0.93156588062566326</v>
+        <v>0.91030297567518581</v>
       </c>
       <c r="D165" s="0" t="s">
         <v>9</v>
       </c>
       <c r="E165" s="0">
-        <v>92.395652789294815</v>
+        <v>50.653224546497434</v>
       </c>
     </row>
     <row r="166">
@@ -2941,16 +2962,16 @@
         <v>1</v>
       </c>
       <c r="B166" s="0">
+        <v>25</v>
+      </c>
+      <c r="C166" s="0">
+        <v>0.91030297567518581</v>
+      </c>
+      <c r="D166" s="0" t="s">
         <v>21</v>
       </c>
-      <c r="C166" s="0">
-        <v>0.93156588062566326</v>
-      </c>
-      <c r="D166" s="0" t="s">
-        <v>12</v>
-      </c>
       <c r="E166" s="0">
-        <v>35.784730427610526</v>
+        <v>32.516127049580952</v>
       </c>
     </row>
     <row r="167">
@@ -2958,16 +2979,16 @@
         <v>1</v>
       </c>
       <c r="B167" s="0">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C167" s="0">
-        <v>0.93156588062566326</v>
+        <v>0.91030297567518581</v>
       </c>
       <c r="D167" s="0" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="E167" s="0">
-        <v>4.9495973437065688</v>
+        <v>31.916666593740416</v>
       </c>
     </row>
     <row r="168">
@@ -2975,16 +2996,16 @@
         <v>1</v>
       </c>
       <c r="B168" s="0">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C168" s="0">
-        <v>0.93156588062566326</v>
+        <v>0.91030297567518581</v>
       </c>
       <c r="D168" s="0" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E168" s="0">
-        <v>3.9864690141850634</v>
+        <v>14.995477942090504</v>
       </c>
     </row>
     <row r="169">
@@ -2992,16 +3013,16 @@
         <v>1</v>
       </c>
       <c r="B169" s="0">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C169" s="0">
-        <v>0.93156588062566326</v>
+        <v>0.91030297567518581</v>
       </c>
       <c r="D169" s="0" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E169" s="0">
-        <v>3.2078877395413512</v>
+        <v>13.930110368664778</v>
       </c>
     </row>
     <row r="170">
@@ -3009,16 +3030,16 @@
         <v>1</v>
       </c>
       <c r="B170" s="0">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C170" s="0">
-        <v>0.93156588062566326</v>
+        <v>0.91030297567518581</v>
       </c>
       <c r="D170" s="0" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E170" s="0">
-        <v>3.1155687107829482</v>
+        <v>3.8325174511657654</v>
       </c>
     </row>
     <row r="171">
@@ -3026,16 +3047,16 @@
         <v>1</v>
       </c>
       <c r="B171" s="0">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C171" s="0">
-        <v>0.93156588062566326</v>
+        <v>0.91030297567518581</v>
       </c>
       <c r="D171" s="0" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="E171" s="0">
-        <v>3.0639746983070659</v>
+        <v>2.0031298320634501</v>
       </c>
     </row>
     <row r="172">
@@ -3043,16 +3064,16 @@
         <v>1</v>
       </c>
       <c r="B172" s="0">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C172" s="0">
-        <v>0.93396132300355572</v>
+        <v>0.91012977849014176</v>
       </c>
       <c r="D172" s="0" t="s">
         <v>8</v>
       </c>
       <c r="E172" s="0">
-        <v>137.34466183758627</v>
+        <v>124.62921941274857</v>
       </c>
     </row>
     <row r="173">
@@ -3060,16 +3081,16 @@
         <v>1</v>
       </c>
       <c r="B173" s="0">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C173" s="0">
-        <v>0.93396132300355572</v>
+        <v>0.91012977849014176</v>
       </c>
       <c r="D173" s="0" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E173" s="0">
-        <v>100.88789274651378</v>
+        <v>88.714482296938471</v>
       </c>
     </row>
     <row r="174">
@@ -3077,16 +3098,16 @@
         <v>1</v>
       </c>
       <c r="B174" s="0">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C174" s="0">
-        <v>0.93396132300355572</v>
+        <v>0.91012977849014176</v>
       </c>
       <c r="D174" s="0" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E174" s="0">
-        <v>88.073621289661602</v>
+        <v>86.598181491809427</v>
       </c>
     </row>
     <row r="175">
@@ -3094,16 +3115,16 @@
         <v>1</v>
       </c>
       <c r="B175" s="0">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C175" s="0">
-        <v>0.93396132300355572</v>
+        <v>0.91012977849014176</v>
       </c>
       <c r="D175" s="0" t="s">
         <v>9</v>
       </c>
       <c r="E175" s="0">
-        <v>79.401123121024497</v>
+        <v>45.192183242538157</v>
       </c>
     </row>
     <row r="176">
@@ -3111,16 +3132,16 @@
         <v>1</v>
       </c>
       <c r="B176" s="0">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C176" s="0">
-        <v>0.93396132300355572</v>
+        <v>0.91012977849014176</v>
       </c>
       <c r="D176" s="0" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="E176" s="0">
-        <v>32.860813786985837</v>
+        <v>32.072147334944795</v>
       </c>
     </row>
     <row r="177">
@@ -3128,16 +3149,16 @@
         <v>1</v>
       </c>
       <c r="B177" s="0">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C177" s="0">
-        <v>0.93396132300355572</v>
+        <v>0.91012977849014176</v>
       </c>
       <c r="D177" s="0" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E177" s="0">
-        <v>5.1566864040657894</v>
+        <v>31.522808286304759</v>
       </c>
     </row>
     <row r="178">
@@ -3145,16 +3166,16 @@
         <v>1</v>
       </c>
       <c r="B178" s="0">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C178" s="0">
-        <v>0.93396132300355572</v>
+        <v>0.91012977849014176</v>
       </c>
       <c r="D178" s="0" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E178" s="0">
-        <v>4.4987101257468609</v>
+        <v>17.075810287507217</v>
       </c>
     </row>
     <row r="179">
@@ -3162,16 +3183,16 @@
         <v>1</v>
       </c>
       <c r="B179" s="0">
+        <v>26</v>
+      </c>
+      <c r="C179" s="0">
+        <v>0.91012977849014176</v>
+      </c>
+      <c r="D179" s="0" t="s">
         <v>23</v>
       </c>
-      <c r="C179" s="0">
-        <v>0.93396132300355572</v>
-      </c>
-      <c r="D179" s="0" t="s">
-        <v>18</v>
-      </c>
       <c r="E179" s="0">
-        <v>4.2502151188125818</v>
+        <v>7.9052475567506315</v>
       </c>
     </row>
     <row r="180">
@@ -3179,16 +3200,16 @@
         <v>1</v>
       </c>
       <c r="B180" s="0">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C180" s="0">
-        <v>0.93396132300355572</v>
+        <v>0.91012977849014176</v>
       </c>
       <c r="D180" s="0" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="E180" s="0">
-        <v>3.2591763376055205</v>
+        <v>1.8505144833782139</v>
       </c>
     </row>
     <row r="181">
@@ -3196,186 +3217,186 @@
         <v>1</v>
       </c>
       <c r="B181" s="0">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C181" s="0">
-        <v>0.93396132300355572</v>
+        <v>0.91012977849014176</v>
       </c>
       <c r="D181" s="0" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E181" s="0">
-        <v>3.1118441566548811</v>
+        <v>1.6060327220630441</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="0" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B182" s="0">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C182" s="0">
-        <v>0.91000857937081214</v>
+        <v>0.93640609336734892</v>
       </c>
       <c r="D182" s="0" t="s">
         <v>8</v>
       </c>
       <c r="E182" s="0">
-        <v>7.3856799770090724</v>
+        <v>131.36926412311325</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="0" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B183" s="0">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C183" s="0">
-        <v>0.91000857937081214</v>
+        <v>0.93640609336734892</v>
       </c>
       <c r="D183" s="0" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E183" s="0">
-        <v>1.7217211013329157</v>
+        <v>96.664772683922777</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="0" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B184" s="0">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C184" s="0">
-        <v>0.91000857937081214</v>
+        <v>0.93640609336734892</v>
       </c>
       <c r="D184" s="0" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E184" s="0">
-        <v>0.44798376201577794</v>
+        <v>83.551273188782176</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="0" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B185" s="0">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C185" s="0">
-        <v>0.91000857937081214</v>
+        <v>0.93640609336734892</v>
       </c>
       <c r="D185" s="0" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E185" s="0">
-        <v>0.41410902368815206</v>
+        <v>60.022683450420679</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="0" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B186" s="0">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C186" s="0">
-        <v>0.91000857937081214</v>
+        <v>0.93640609336734892</v>
       </c>
       <c r="D186" s="0" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="E186" s="0">
-        <v>0.21074277045722067</v>
+        <v>39.854056048591708</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="0" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B187" s="0">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C187" s="0">
-        <v>0.91000857937081214</v>
+        <v>0.93640609336734892</v>
       </c>
       <c r="D187" s="0" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E187" s="0">
-        <v>0.088038967125618581</v>
+        <v>18.373106502900942</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="0" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B188" s="0">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C188" s="0">
-        <v>0.91000857937081214</v>
+        <v>0.93640609336734892</v>
       </c>
       <c r="D188" s="0" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="E188" s="0">
-        <v>0.068505207513125624</v>
+        <v>9.5064125697127277</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="0" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B189" s="0">
+        <v>27</v>
+      </c>
+      <c r="C189" s="0">
+        <v>0.93640609336734892</v>
+      </c>
+      <c r="D189" s="0" t="s">
         <v>23</v>
       </c>
-      <c r="C189" s="0">
-        <v>0.91000857937081214</v>
-      </c>
-      <c r="D189" s="0" t="s">
-        <v>16</v>
-      </c>
       <c r="E189" s="0">
-        <v>0.061766961105963164</v>
+        <v>9.1984276308954467</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="0" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B190" s="0">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C190" s="0">
-        <v>0.91000857937081214</v>
+        <v>0.93640609336734892</v>
       </c>
       <c r="D190" s="0" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E190" s="0">
-        <v>0.051811931249418831</v>
+        <v>3.7226974923338867</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="0" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B191" s="0">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C191" s="0">
-        <v>0.91000857937081214</v>
+        <v>0.93640609336734892</v>
       </c>
       <c r="D191" s="0" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="E191" s="0">
-        <v>0.034897325482964446</v>
+        <v>2.4937597922439436</v>
       </c>
     </row>
     <row r="192">
@@ -3383,16 +3404,16 @@
         <v>1</v>
       </c>
       <c r="B192" s="0">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C192" s="0">
-        <v>0.91287050097820388</v>
+        <v>0.90077469204015748</v>
       </c>
       <c r="D192" s="0" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E192" s="0">
-        <v>132.08289000368165</v>
+        <v>129.64835220661541</v>
       </c>
     </row>
     <row r="193">
@@ -3400,16 +3421,16 @@
         <v>1</v>
       </c>
       <c r="B193" s="0">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C193" s="0">
-        <v>0.91287050097820388</v>
+        <v>0.90077469204015748</v>
       </c>
       <c r="D193" s="0" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E193" s="0">
-        <v>121.15890055879862</v>
+        <v>114.81762811440608</v>
       </c>
     </row>
     <row r="194">
@@ -3417,16 +3438,16 @@
         <v>1</v>
       </c>
       <c r="B194" s="0">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C194" s="0">
-        <v>0.91287050097820388</v>
+        <v>0.90077469204015748</v>
       </c>
       <c r="D194" s="0" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E194" s="0">
-        <v>86.309668607816732</v>
+        <v>93.173450495841266</v>
       </c>
     </row>
     <row r="195">
@@ -3434,16 +3455,16 @@
         <v>1</v>
       </c>
       <c r="B195" s="0">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C195" s="0">
-        <v>0.91287050097820388</v>
+        <v>0.90077469204015748</v>
       </c>
       <c r="D195" s="0" t="s">
         <v>9</v>
       </c>
       <c r="E195" s="0">
-        <v>77.623500553829643</v>
+        <v>39.22203447493407</v>
       </c>
     </row>
     <row r="196">
@@ -3451,16 +3472,16 @@
         <v>1</v>
       </c>
       <c r="B196" s="0">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C196" s="0">
-        <v>0.91287050097820388</v>
+        <v>0.90077469204015748</v>
       </c>
       <c r="D196" s="0" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="E196" s="0">
-        <v>40.104643567294474</v>
+        <v>24.568485342927165</v>
       </c>
     </row>
     <row r="197">
@@ -3468,16 +3489,16 @@
         <v>1</v>
       </c>
       <c r="B197" s="0">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C197" s="0">
-        <v>0.91287050097820388</v>
+        <v>0.90077469204015748</v>
       </c>
       <c r="D197" s="0" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E197" s="0">
-        <v>3.3278149978754623</v>
+        <v>24.244228120662516</v>
       </c>
     </row>
     <row r="198">
@@ -3485,16 +3506,16 @@
         <v>1</v>
       </c>
       <c r="B198" s="0">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C198" s="0">
-        <v>0.91287050097820388</v>
+        <v>0.90077469204015748</v>
       </c>
       <c r="D198" s="0" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E198" s="0">
-        <v>3.2674345556942881</v>
+        <v>17.243913404275386</v>
       </c>
     </row>
     <row r="199">
@@ -3502,16 +3523,16 @@
         <v>1</v>
       </c>
       <c r="B199" s="0">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C199" s="0">
-        <v>0.91287050097820388</v>
+        <v>0.90077469204015748</v>
       </c>
       <c r="D199" s="0" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="E199" s="0">
-        <v>2.9652570715275659</v>
+        <v>7.246681722822216</v>
       </c>
     </row>
     <row r="200">
@@ -3519,16 +3540,16 @@
         <v>1</v>
       </c>
       <c r="B200" s="0">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C200" s="0">
-        <v>0.91287050097820388</v>
+        <v>0.90077469204015748</v>
       </c>
       <c r="D200" s="0" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="E200" s="0">
-        <v>2.7569579872697041</v>
+        <v>2.5174976223215104</v>
       </c>
     </row>
     <row r="201">
@@ -3536,16 +3557,16 @@
         <v>1</v>
       </c>
       <c r="B201" s="0">
+        <v>28</v>
+      </c>
+      <c r="C201" s="0">
+        <v>0.90077469204015748</v>
+      </c>
+      <c r="D201" s="0" t="s">
         <v>25</v>
       </c>
-      <c r="C201" s="0">
-        <v>0.91287050097820388</v>
-      </c>
-      <c r="D201" s="0" t="s">
-        <v>18</v>
-      </c>
       <c r="E201" s="0">
-        <v>2.7084597597516238</v>
+        <v>1.8056607807912541</v>
       </c>
     </row>
     <row r="202">
@@ -3556,13 +3577,13 @@
         <v>29</v>
       </c>
       <c r="C202" s="0">
-        <v>0.90656932849293448</v>
+        <v>0.90075331661320068</v>
       </c>
       <c r="D202" s="0" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E202" s="0">
-        <v>122.55985553665204</v>
+        <v>121.5319640280545</v>
       </c>
     </row>
     <row r="203">
@@ -3573,13 +3594,13 @@
         <v>29</v>
       </c>
       <c r="C203" s="0">
-        <v>0.90656932849293448</v>
+        <v>0.90075331661320068</v>
       </c>
       <c r="D203" s="0" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E203" s="0">
-        <v>112.71124764736221</v>
+        <v>104.7269477203717</v>
       </c>
     </row>
     <row r="204">
@@ -3590,13 +3611,13 @@
         <v>29</v>
       </c>
       <c r="C204" s="0">
-        <v>0.90656932849293448</v>
+        <v>0.90075331661320068</v>
       </c>
       <c r="D204" s="0" t="s">
         <v>7</v>
       </c>
       <c r="E204" s="0">
-        <v>100.75810576660817</v>
+        <v>86.569318497612528</v>
       </c>
     </row>
     <row r="205">
@@ -3607,13 +3628,13 @@
         <v>29</v>
       </c>
       <c r="C205" s="0">
-        <v>0.90656932849293448</v>
+        <v>0.90075331661320068</v>
       </c>
       <c r="D205" s="0" t="s">
         <v>9</v>
       </c>
       <c r="E205" s="0">
-        <v>62.547199025192228</v>
+        <v>56.208778365391701</v>
       </c>
     </row>
     <row r="206">
@@ -3624,13 +3645,13 @@
         <v>29</v>
       </c>
       <c r="C206" s="0">
-        <v>0.90656932849293448</v>
+        <v>0.90075331661320068</v>
       </c>
       <c r="D206" s="0" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="E206" s="0">
-        <v>35.843776048015997</v>
+        <v>34.951967524891138</v>
       </c>
     </row>
     <row r="207">
@@ -3641,13 +3662,13 @@
         <v>29</v>
       </c>
       <c r="C207" s="0">
-        <v>0.90656932849293448</v>
+        <v>0.90075331661320068</v>
       </c>
       <c r="D207" s="0" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="E207" s="0">
-        <v>4.4294692280842467</v>
+        <v>21.266265926668954</v>
       </c>
     </row>
     <row r="208">
@@ -3658,13 +3679,13 @@
         <v>29</v>
       </c>
       <c r="C208" s="0">
-        <v>0.90656932849293448</v>
+        <v>0.90075331661320068</v>
       </c>
       <c r="D208" s="0" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E208" s="0">
-        <v>3.8564187042543754</v>
+        <v>17.133176807925778</v>
       </c>
     </row>
     <row r="209">
@@ -3675,13 +3696,13 @@
         <v>29</v>
       </c>
       <c r="C209" s="0">
-        <v>0.90656932849293448</v>
+        <v>0.90075331661320068</v>
       </c>
       <c r="D209" s="0" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E209" s="0">
-        <v>3.4646877081648841</v>
+        <v>9.8628961719522934</v>
       </c>
     </row>
     <row r="210">
@@ -3692,13 +3713,13 @@
         <v>29</v>
       </c>
       <c r="C210" s="0">
-        <v>0.90656932849293448</v>
+        <v>0.90075331661320068</v>
       </c>
       <c r="D210" s="0" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E210" s="0">
-        <v>2.4645149003875555</v>
+        <v>4.3046934863607014</v>
       </c>
     </row>
     <row r="211">
@@ -3709,13 +3730,13 @@
         <v>29</v>
       </c>
       <c r="C211" s="0">
-        <v>0.90656932849293448</v>
+        <v>0.90075331661320068</v>
       </c>
       <c r="D211" s="0" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="E211" s="0">
-        <v>2.4484343832340012</v>
+        <v>1.7944382125454197</v>
       </c>
     </row>
     <row r="212">
@@ -3723,16 +3744,16 @@
         <v>1</v>
       </c>
       <c r="B212" s="0">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C212" s="0">
-        <v>0.92689854707431074</v>
+        <v>0.94223416644852975</v>
       </c>
       <c r="D212" s="0" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E212" s="0">
-        <v>134.56725230355917</v>
+        <v>104.9010786684796</v>
       </c>
     </row>
     <row r="213">
@@ -3740,16 +3761,16 @@
         <v>1</v>
       </c>
       <c r="B213" s="0">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C213" s="0">
-        <v>0.92689854707431074</v>
+        <v>0.94223416644852975</v>
       </c>
       <c r="D213" s="0" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E213" s="0">
-        <v>132.87981874088618</v>
+        <v>97.481270656436934</v>
       </c>
     </row>
     <row r="214">
@@ -3757,16 +3778,16 @@
         <v>1</v>
       </c>
       <c r="B214" s="0">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C214" s="0">
-        <v>0.92689854707431074</v>
+        <v>0.94223416644852975</v>
       </c>
       <c r="D214" s="0" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E214" s="0">
-        <v>105.52792995401295</v>
+        <v>95.578059869104479</v>
       </c>
     </row>
     <row r="215">
@@ -3774,16 +3795,16 @@
         <v>1</v>
       </c>
       <c r="B215" s="0">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C215" s="0">
-        <v>0.92689854707431074</v>
+        <v>0.94223416644852975</v>
       </c>
       <c r="D215" s="0" t="s">
         <v>9</v>
       </c>
       <c r="E215" s="0">
-        <v>68.220580529661476</v>
+        <v>56.619739581628416</v>
       </c>
     </row>
     <row r="216">
@@ -3791,16 +3812,16 @@
         <v>1</v>
       </c>
       <c r="B216" s="0">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C216" s="0">
-        <v>0.92689854707431074</v>
+        <v>0.94223416644852975</v>
       </c>
       <c r="D216" s="0" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="E216" s="0">
-        <v>31.317577317520307</v>
+        <v>24.647266018043538</v>
       </c>
     </row>
     <row r="217">
@@ -3808,16 +3829,16 @@
         <v>1</v>
       </c>
       <c r="B217" s="0">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C217" s="0">
-        <v>0.92689854707431074</v>
+        <v>0.94223416644852975</v>
       </c>
       <c r="D217" s="0" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="E217" s="0">
-        <v>5.7653888689991755</v>
+        <v>17.235738087389887</v>
       </c>
     </row>
     <row r="218">
@@ -3825,16 +3846,16 @@
         <v>1</v>
       </c>
       <c r="B218" s="0">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C218" s="0">
-        <v>0.92689854707431074</v>
+        <v>0.94223416644852975</v>
       </c>
       <c r="D218" s="0" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E218" s="0">
-        <v>5.1618285314706016</v>
+        <v>16.095608064135739</v>
       </c>
     </row>
     <row r="219">
@@ -3842,16 +3863,16 @@
         <v>1</v>
       </c>
       <c r="B219" s="0">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C219" s="0">
-        <v>0.92689854707431074</v>
+        <v>0.94223416644852975</v>
       </c>
       <c r="D219" s="0" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="E219" s="0">
-        <v>3.4112842914258699</v>
+        <v>8.2402928282018166</v>
       </c>
     </row>
     <row r="220">
@@ -3859,16 +3880,16 @@
         <v>1</v>
       </c>
       <c r="B220" s="0">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C220" s="0">
-        <v>0.92689854707431074</v>
+        <v>0.94223416644852975</v>
       </c>
       <c r="D220" s="0" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E220" s="0">
-        <v>3.2093626662271708</v>
+        <v>2.6748900029363489</v>
       </c>
     </row>
     <row r="221">
@@ -3876,16 +3897,16 @@
         <v>1</v>
       </c>
       <c r="B221" s="0">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C221" s="0">
-        <v>0.92689854707431074</v>
+        <v>0.94223416644852975</v>
       </c>
       <c r="D221" s="0" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E221" s="0">
-        <v>1.8262348513445716</v>
+        <v>2.3691920115909424</v>
       </c>
     </row>
     <row r="222">
@@ -3896,13 +3917,13 @@
         <v>32</v>
       </c>
       <c r="C222" s="0">
-        <v>0.9383595643565612</v>
+        <v>0.93404921347527625</v>
       </c>
       <c r="D222" s="0" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E222" s="0">
-        <v>121.02914457453569</v>
+        <v>136.80300081874555</v>
       </c>
     </row>
     <row r="223">
@@ -3913,13 +3934,13 @@
         <v>32</v>
       </c>
       <c r="C223" s="0">
-        <v>0.9383595643565612</v>
+        <v>0.93404921347527625</v>
       </c>
       <c r="D223" s="0" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E223" s="0">
-        <v>105.86366285782448</v>
+        <v>97.096408604647806</v>
       </c>
     </row>
     <row r="224">
@@ -3930,13 +3951,13 @@
         <v>32</v>
       </c>
       <c r="C224" s="0">
-        <v>0.9383595643565612</v>
+        <v>0.93404921347527625</v>
       </c>
       <c r="D224" s="0" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E224" s="0">
-        <v>95.08366965686713</v>
+        <v>70.28061409577424</v>
       </c>
     </row>
     <row r="225">
@@ -3947,13 +3968,13 @@
         <v>32</v>
       </c>
       <c r="C225" s="0">
-        <v>0.9383595643565612</v>
+        <v>0.93404921347527625</v>
       </c>
       <c r="D225" s="0" t="s">
         <v>9</v>
       </c>
       <c r="E225" s="0">
-        <v>64.873008701041783</v>
+        <v>56.608826205539486</v>
       </c>
     </row>
     <row r="226">
@@ -3964,13 +3985,13 @@
         <v>32</v>
       </c>
       <c r="C226" s="0">
-        <v>0.9383595643565612</v>
+        <v>0.93404921347527625</v>
       </c>
       <c r="D226" s="0" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="E226" s="0">
-        <v>24.542482694767354</v>
+        <v>48.827640015186354</v>
       </c>
     </row>
     <row r="227">
@@ -3981,13 +4002,13 @@
         <v>32</v>
       </c>
       <c r="C227" s="0">
-        <v>0.9383595643565612</v>
+        <v>0.93404921347527625</v>
       </c>
       <c r="D227" s="0" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="E227" s="0">
-        <v>6.0724649137182505</v>
+        <v>20.333568595876578</v>
       </c>
     </row>
     <row r="228">
@@ -3998,13 +4019,13 @@
         <v>32</v>
       </c>
       <c r="C228" s="0">
-        <v>0.9383595643565612</v>
+        <v>0.93404921347527625</v>
       </c>
       <c r="D228" s="0" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="E228" s="0">
-        <v>4.3980929907991513</v>
+        <v>16.639857407298301</v>
       </c>
     </row>
     <row r="229">
@@ -4015,13 +4036,13 @@
         <v>32</v>
       </c>
       <c r="C229" s="0">
-        <v>0.9383595643565612</v>
+        <v>0.93404921347527625</v>
       </c>
       <c r="D229" s="0" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="E229" s="0">
-        <v>3.3955511878181586</v>
+        <v>6.6773263349205596</v>
       </c>
     </row>
     <row r="230">
@@ -4032,13 +4053,13 @@
         <v>32</v>
       </c>
       <c r="C230" s="0">
-        <v>0.9383595643565612</v>
+        <v>0.93404921347527625</v>
       </c>
       <c r="D230" s="0" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E230" s="0">
-        <v>2.9795056443679546</v>
+        <v>2.9814394661709285</v>
       </c>
     </row>
     <row r="231">
@@ -4049,13 +4070,13 @@
         <v>32</v>
       </c>
       <c r="C231" s="0">
-        <v>0.9383595643565612</v>
+        <v>0.93404921347527625</v>
       </c>
       <c r="D231" s="0" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="E231" s="0">
-        <v>2.7496347612642671</v>
+        <v>2.5833494385067941</v>
       </c>
     </row>
     <row r="232">
@@ -4063,16 +4084,16 @@
         <v>1</v>
       </c>
       <c r="B232" s="0">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C232" s="0">
-        <v>0.90368865517415564</v>
+        <v>0.9012848720930694</v>
       </c>
       <c r="D232" s="0" t="s">
         <v>8</v>
       </c>
       <c r="E232" s="0">
-        <v>140.51846710415333</v>
+        <v>125.17647125656772</v>
       </c>
     </row>
     <row r="233">
@@ -4080,16 +4101,16 @@
         <v>1</v>
       </c>
       <c r="B233" s="0">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C233" s="0">
-        <v>0.90368865517415564</v>
+        <v>0.9012848720930694</v>
       </c>
       <c r="D233" s="0" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E233" s="0">
-        <v>118.5230946432771</v>
+        <v>109.93967154797281</v>
       </c>
     </row>
     <row r="234">
@@ -4097,16 +4118,16 @@
         <v>1</v>
       </c>
       <c r="B234" s="0">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C234" s="0">
-        <v>0.90368865517415564</v>
+        <v>0.9012848720930694</v>
       </c>
       <c r="D234" s="0" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E234" s="0">
-        <v>92.209407797255167</v>
+        <v>72.861981383244697</v>
       </c>
     </row>
     <row r="235">
@@ -4114,16 +4135,16 @@
         <v>1</v>
       </c>
       <c r="B235" s="0">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C235" s="0">
-        <v>0.90368865517415564</v>
+        <v>0.9012848720930694</v>
       </c>
       <c r="D235" s="0" t="s">
         <v>9</v>
       </c>
       <c r="E235" s="0">
-        <v>80.735329001198366</v>
+        <v>61.56298251305703</v>
       </c>
     </row>
     <row r="236">
@@ -4131,16 +4152,16 @@
         <v>1</v>
       </c>
       <c r="B236" s="0">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C236" s="0">
-        <v>0.90368865517415564</v>
+        <v>0.9012848720930694</v>
       </c>
       <c r="D236" s="0" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="E236" s="0">
-        <v>30.096990600137495</v>
+        <v>38.320727318708457</v>
       </c>
     </row>
     <row r="237">
@@ -4148,16 +4169,16 @@
         <v>1</v>
       </c>
       <c r="B237" s="0">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C237" s="0">
-        <v>0.90368865517415564</v>
+        <v>0.9012848720930694</v>
       </c>
       <c r="D237" s="0" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E237" s="0">
-        <v>4.9197845903734105</v>
+        <v>20.909816121328653</v>
       </c>
     </row>
     <row r="238">
@@ -4165,16 +4186,16 @@
         <v>1</v>
       </c>
       <c r="B238" s="0">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C238" s="0">
-        <v>0.90368865517415564</v>
+        <v>0.9012848720930694</v>
       </c>
       <c r="D238" s="0" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E238" s="0">
-        <v>4.6789887100260152</v>
+        <v>20.037467177925947</v>
       </c>
     </row>
     <row r="239">
@@ -4182,16 +4203,16 @@
         <v>1</v>
       </c>
       <c r="B239" s="0">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C239" s="0">
-        <v>0.90368865517415564</v>
+        <v>0.9012848720930694</v>
       </c>
       <c r="D239" s="0" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E239" s="0">
-        <v>3.5401934716954311</v>
+        <v>4.4914769979743161</v>
       </c>
     </row>
     <row r="240">
@@ -4199,16 +4220,16 @@
         <v>1</v>
       </c>
       <c r="B240" s="0">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C240" s="0">
-        <v>0.90368865517415564</v>
+        <v>0.9012848720930694</v>
       </c>
       <c r="D240" s="0" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E240" s="0">
-        <v>3.2875860499553</v>
+        <v>3.0002165200880238</v>
       </c>
     </row>
     <row r="241">
@@ -4216,16 +4237,16 @@
         <v>1</v>
       </c>
       <c r="B241" s="0">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C241" s="0">
-        <v>0.90368865517415564</v>
+        <v>0.9012848720930694</v>
       </c>
       <c r="D241" s="0" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E241" s="0">
-        <v>2.6119541015262824</v>
+        <v>2.4286843187870688</v>
       </c>
     </row>
     <row r="242">
@@ -4233,16 +4254,16 @@
         <v>1</v>
       </c>
       <c r="B242" s="0">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C242" s="0">
-        <v>0.90488805736421085</v>
+        <v>0.92586836695472574</v>
       </c>
       <c r="D242" s="0" t="s">
         <v>8</v>
       </c>
       <c r="E242" s="0">
-        <v>154.15797076179334</v>
+        <v>104.51889916441191</v>
       </c>
     </row>
     <row r="243">
@@ -4250,16 +4271,16 @@
         <v>1</v>
       </c>
       <c r="B243" s="0">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C243" s="0">
-        <v>0.90488805736421085</v>
+        <v>0.92586836695472574</v>
       </c>
       <c r="D243" s="0" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E243" s="0">
-        <v>95.867206304508088</v>
+        <v>95.890255567039858</v>
       </c>
     </row>
     <row r="244">
@@ -4267,16 +4288,16 @@
         <v>1</v>
       </c>
       <c r="B244" s="0">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C244" s="0">
-        <v>0.90488805736421085</v>
+        <v>0.92586836695472574</v>
       </c>
       <c r="D244" s="0" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E244" s="0">
-        <v>92.773928495220559</v>
+        <v>85.128347377845543</v>
       </c>
     </row>
     <row r="245">
@@ -4284,16 +4305,16 @@
         <v>1</v>
       </c>
       <c r="B245" s="0">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C245" s="0">
-        <v>0.90488805736421085</v>
+        <v>0.92586836695472574</v>
       </c>
       <c r="D245" s="0" t="s">
         <v>9</v>
       </c>
       <c r="E245" s="0">
-        <v>67.433541514562762</v>
+        <v>65.452767138940629</v>
       </c>
     </row>
     <row r="246">
@@ -4301,16 +4322,16 @@
         <v>1</v>
       </c>
       <c r="B246" s="0">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C246" s="0">
-        <v>0.90488805736421085</v>
+        <v>0.92586836695472574</v>
       </c>
       <c r="D246" s="0" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="E246" s="0">
-        <v>25.762575701147561</v>
+        <v>31.515532702695424</v>
       </c>
     </row>
     <row r="247">
@@ -4318,16 +4339,16 @@
         <v>1</v>
       </c>
       <c r="B247" s="0">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C247" s="0">
-        <v>0.90488805736421085</v>
+        <v>0.92586836695472574</v>
       </c>
       <c r="D247" s="0" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E247" s="0">
-        <v>5.2308744411752057</v>
+        <v>22.602561150565002</v>
       </c>
     </row>
     <row r="248">
@@ -4335,16 +4356,16 @@
         <v>1</v>
       </c>
       <c r="B248" s="0">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C248" s="0">
-        <v>0.90488805736421085</v>
+        <v>0.92586836695472574</v>
       </c>
       <c r="D248" s="0" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="E248" s="0">
-        <v>4.4675820734133431</v>
+        <v>22.249111515924191</v>
       </c>
     </row>
     <row r="249">
@@ -4352,16 +4373,16 @@
         <v>1</v>
       </c>
       <c r="B249" s="0">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C249" s="0">
-        <v>0.90488805736421085</v>
+        <v>0.92586836695472574</v>
       </c>
       <c r="D249" s="0" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="E249" s="0">
-        <v>3.7867972412874367</v>
+        <v>6.4504651680045058</v>
       </c>
     </row>
     <row r="250">
@@ -4369,16 +4390,16 @@
         <v>1</v>
       </c>
       <c r="B250" s="0">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C250" s="0">
-        <v>0.90488805736421085</v>
+        <v>0.92586836695472574</v>
       </c>
       <c r="D250" s="0" t="s">
         <v>13</v>
       </c>
       <c r="E250" s="0">
-        <v>3.6681896222869583</v>
+        <v>3.0239019741816673</v>
       </c>
     </row>
     <row r="251">
@@ -4386,16 +4407,16 @@
         <v>1</v>
       </c>
       <c r="B251" s="0">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C251" s="0">
-        <v>0.90488805736421085</v>
+        <v>0.92586836695472574</v>
       </c>
       <c r="D251" s="0" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="E251" s="0">
-        <v>3.0824146592992223</v>
+        <v>1.9351708259838489</v>
       </c>
     </row>
     <row r="252">
@@ -4403,16 +4424,16 @@
         <v>1</v>
       </c>
       <c r="B252" s="0">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="C252" s="0">
-        <v>0.93255641799744993</v>
+        <v>0.93378479826680649</v>
       </c>
       <c r="D252" s="0" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E252" s="0">
-        <v>127.63758697842567</v>
+        <v>130.45149764098977</v>
       </c>
     </row>
     <row r="253">
@@ -4420,16 +4441,16 @@
         <v>1</v>
       </c>
       <c r="B253" s="0">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="C253" s="0">
-        <v>0.93255641799744993</v>
+        <v>0.93378479826680649</v>
       </c>
       <c r="D253" s="0" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E253" s="0">
-        <v>92.125333429592175</v>
+        <v>101.47887153130658</v>
       </c>
     </row>
     <row r="254">
@@ -4437,16 +4458,16 @@
         <v>1</v>
       </c>
       <c r="B254" s="0">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="C254" s="0">
-        <v>0.93255641799744993</v>
+        <v>0.93378479826680649</v>
       </c>
       <c r="D254" s="0" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E254" s="0">
-        <v>85.101080710255133</v>
+        <v>93.517379514967743</v>
       </c>
     </row>
     <row r="255">
@@ -4454,16 +4475,16 @@
         <v>1</v>
       </c>
       <c r="B255" s="0">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="C255" s="0">
-        <v>0.93255641799744993</v>
+        <v>0.93378479826680649</v>
       </c>
       <c r="D255" s="0" t="s">
         <v>9</v>
       </c>
       <c r="E255" s="0">
-        <v>80.074120849938765</v>
+        <v>55.703685729582418</v>
       </c>
     </row>
     <row r="256">
@@ -4471,16 +4492,16 @@
         <v>1</v>
       </c>
       <c r="B256" s="0">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="C256" s="0">
-        <v>0.93255641799744993</v>
+        <v>0.93378479826680649</v>
       </c>
       <c r="D256" s="0" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="E256" s="0">
-        <v>32.778951948501792</v>
+        <v>24.295253899992478</v>
       </c>
     </row>
     <row r="257">
@@ -4488,16 +4509,16 @@
         <v>1</v>
       </c>
       <c r="B257" s="0">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="C257" s="0">
-        <v>0.93255641799744993</v>
+        <v>0.93378479826680649</v>
       </c>
       <c r="D257" s="0" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="E257" s="0">
-        <v>5.6697810653439831</v>
+        <v>21.473264521774439</v>
       </c>
     </row>
     <row r="258">
@@ -4505,16 +4526,16 @@
         <v>1</v>
       </c>
       <c r="B258" s="0">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="C258" s="0">
-        <v>0.93255641799744993</v>
+        <v>0.93378479826680649</v>
       </c>
       <c r="D258" s="0" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E258" s="0">
-        <v>4.7010996368025664</v>
+        <v>16.278043215010797</v>
       </c>
     </row>
     <row r="259">
@@ -4522,16 +4543,16 @@
         <v>1</v>
       </c>
       <c r="B259" s="0">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="C259" s="0">
-        <v>0.93255641799744993</v>
+        <v>0.93378479826680649</v>
       </c>
       <c r="D259" s="0" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="E259" s="0">
-        <v>3.6295136587570496</v>
+        <v>8.0433450639797428</v>
       </c>
     </row>
     <row r="260">
@@ -4539,16 +4560,16 @@
         <v>1</v>
       </c>
       <c r="B260" s="0">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="C260" s="0">
-        <v>0.93255641799744993</v>
+        <v>0.93378479826680649</v>
       </c>
       <c r="D260" s="0" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E260" s="0">
-        <v>2.9627811279148748</v>
+        <v>2.0594542885972613</v>
       </c>
     </row>
     <row r="261">
@@ -4556,16 +4577,16 @@
         <v>1</v>
       </c>
       <c r="B261" s="0">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="C261" s="0">
-        <v>0.93255641799744993</v>
+        <v>0.93378479826680649</v>
       </c>
       <c r="D261" s="0" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="E261" s="0">
-        <v>2.3052427762066956</v>
+        <v>2.0387616193218552</v>
       </c>
     </row>
     <row r="262">
@@ -4573,16 +4594,16 @@
         <v>1</v>
       </c>
       <c r="B262" s="0">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="C262" s="0">
-        <v>0.90416102951178001</v>
+        <v>0.91891122531897584</v>
       </c>
       <c r="D262" s="0" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E262" s="0">
-        <v>127.70340370987725</v>
+        <v>107.9474516004517</v>
       </c>
     </row>
     <row r="263">
@@ -4590,16 +4611,16 @@
         <v>1</v>
       </c>
       <c r="B263" s="0">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="C263" s="0">
-        <v>0.90416102951178001</v>
+        <v>0.91891122531897584</v>
       </c>
       <c r="D263" s="0" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E263" s="0">
-        <v>124.81719998195045</v>
+        <v>102.29108206973673</v>
       </c>
     </row>
     <row r="264">
@@ -4607,16 +4628,16 @@
         <v>1</v>
       </c>
       <c r="B264" s="0">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="C264" s="0">
-        <v>0.90416102951178001</v>
+        <v>0.91891122531897584</v>
       </c>
       <c r="D264" s="0" t="s">
         <v>8</v>
       </c>
       <c r="E264" s="0">
-        <v>117.01367367146244</v>
+        <v>98.741600754947356</v>
       </c>
     </row>
     <row r="265">
@@ -4624,16 +4645,16 @@
         <v>1</v>
       </c>
       <c r="B265" s="0">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="C265" s="0">
-        <v>0.90416102951178001</v>
+        <v>0.91891122531897584</v>
       </c>
       <c r="D265" s="0" t="s">
         <v>9</v>
       </c>
       <c r="E265" s="0">
-        <v>78.723033403254945</v>
+        <v>82.413163760266286</v>
       </c>
     </row>
     <row r="266">
@@ -4641,16 +4662,16 @@
         <v>1</v>
       </c>
       <c r="B266" s="0">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="C266" s="0">
-        <v>0.90416102951178001</v>
+        <v>0.91891122531897584</v>
       </c>
       <c r="D266" s="0" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="E266" s="0">
-        <v>30.055351257403697</v>
+        <v>32.79062050684535</v>
       </c>
     </row>
     <row r="267">
@@ -4658,16 +4679,16 @@
         <v>1</v>
       </c>
       <c r="B267" s="0">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="C267" s="0">
-        <v>0.90416102951178001</v>
+        <v>0.91891122531897584</v>
       </c>
       <c r="D267" s="0" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E267" s="0">
-        <v>4.2081567632522443</v>
+        <v>22.574876862816367</v>
       </c>
     </row>
     <row r="268">
@@ -4675,16 +4696,16 @@
         <v>1</v>
       </c>
       <c r="B268" s="0">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="C268" s="0">
-        <v>0.90416102951178001</v>
+        <v>0.91891122531897584</v>
       </c>
       <c r="D268" s="0" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E268" s="0">
-        <v>3.2191690389217098</v>
+        <v>16.6479324320985</v>
       </c>
     </row>
     <row r="269">
@@ -4692,16 +4713,16 @@
         <v>1</v>
       </c>
       <c r="B269" s="0">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="C269" s="0">
-        <v>0.90416102951178001</v>
+        <v>0.91891122531897584</v>
       </c>
       <c r="D269" s="0" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E269" s="0">
-        <v>3.2071267512656818</v>
+        <v>11.539165286657592</v>
       </c>
     </row>
     <row r="270">
@@ -4709,16 +4730,16 @@
         <v>1</v>
       </c>
       <c r="B270" s="0">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="C270" s="0">
-        <v>0.90416102951178001</v>
+        <v>0.91891122531897584</v>
       </c>
       <c r="D270" s="0" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E270" s="0">
-        <v>3.0825305096913747</v>
+        <v>2.9550745089180386</v>
       </c>
     </row>
     <row r="271">
@@ -4726,16 +4747,16 @@
         <v>1</v>
       </c>
       <c r="B271" s="0">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="C271" s="0">
-        <v>0.90416102951178001</v>
+        <v>0.91891122531897584</v>
       </c>
       <c r="D271" s="0" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="E271" s="0">
-        <v>2.5690594587700719</v>
+        <v>2.5116921784853288</v>
       </c>
     </row>
     <row r="272">
@@ -4743,16 +4764,16 @@
         <v>1</v>
       </c>
       <c r="B272" s="0">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="C272" s="0">
-        <v>0.92031653001239233</v>
+        <v>0.91189099931417128</v>
       </c>
       <c r="D272" s="0" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E272" s="0">
-        <v>169.83500825269232</v>
+        <v>135.99704442499035</v>
       </c>
     </row>
     <row r="273">
@@ -4760,16 +4781,16 @@
         <v>1</v>
       </c>
       <c r="B273" s="0">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="C273" s="0">
-        <v>0.92031653001239233</v>
+        <v>0.91189099931417128</v>
       </c>
       <c r="D273" s="0" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E273" s="0">
-        <v>94.580627323731619</v>
+        <v>92.261582809476167</v>
       </c>
     </row>
     <row r="274">
@@ -4777,16 +4798,16 @@
         <v>1</v>
       </c>
       <c r="B274" s="0">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="C274" s="0">
-        <v>0.92031653001239233</v>
+        <v>0.91189099931417128</v>
       </c>
       <c r="D274" s="0" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E274" s="0">
-        <v>93.790998981637898</v>
+        <v>87.152379940060527</v>
       </c>
     </row>
     <row r="275">
@@ -4794,16 +4815,16 @@
         <v>1</v>
       </c>
       <c r="B275" s="0">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="C275" s="0">
-        <v>0.92031653001239233</v>
+        <v>0.91189099931417128</v>
       </c>
       <c r="D275" s="0" t="s">
         <v>9</v>
       </c>
       <c r="E275" s="0">
-        <v>87.763308788782581</v>
+        <v>51.494546962589638</v>
       </c>
     </row>
     <row r="276">
@@ -4811,16 +4832,16 @@
         <v>1</v>
       </c>
       <c r="B276" s="0">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="C276" s="0">
-        <v>0.92031653001239233</v>
+        <v>0.91189099931417128</v>
       </c>
       <c r="D276" s="0" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="E276" s="0">
-        <v>37.636617067951327</v>
+        <v>35.124389191441949</v>
       </c>
     </row>
     <row r="277">
@@ -4828,16 +4849,16 @@
         <v>1</v>
       </c>
       <c r="B277" s="0">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="C277" s="0">
-        <v>0.92031653001239233</v>
+        <v>0.91189099931417128</v>
       </c>
       <c r="D277" s="0" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="E277" s="0">
-        <v>10.082960326751573</v>
+        <v>27.455635712939213</v>
       </c>
     </row>
     <row r="278">
@@ -4845,16 +4866,16 @@
         <v>1</v>
       </c>
       <c r="B278" s="0">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="C278" s="0">
-        <v>0.92031653001239233</v>
+        <v>0.91189099931417128</v>
       </c>
       <c r="D278" s="0" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E278" s="0">
-        <v>4.6606417920637382</v>
+        <v>17.511661897789018</v>
       </c>
     </row>
     <row r="279">
@@ -4862,16 +4883,16 @@
         <v>1</v>
       </c>
       <c r="B279" s="0">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="C279" s="0">
-        <v>0.92031653001239233</v>
+        <v>0.91189099931417128</v>
       </c>
       <c r="D279" s="0" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E279" s="0">
-        <v>3.4052894465641907</v>
+        <v>8.8726940285845775</v>
       </c>
     </row>
     <row r="280">
@@ -4879,16 +4900,16 @@
         <v>1</v>
       </c>
       <c r="B280" s="0">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="C280" s="0">
-        <v>0.92031653001239233</v>
+        <v>0.91189099931417128</v>
       </c>
       <c r="D280" s="0" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E280" s="0">
-        <v>3.2493672201838626</v>
+        <v>2.5550536607411489</v>
       </c>
     </row>
     <row r="281">
@@ -4896,16 +4917,16 @@
         <v>1</v>
       </c>
       <c r="B281" s="0">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="C281" s="0">
-        <v>0.92031653001239233</v>
+        <v>0.91189099931417128</v>
       </c>
       <c r="D281" s="0" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="E281" s="0">
-        <v>2.1966544679106272</v>
+        <v>2.3267948918607839</v>
       </c>
     </row>
     <row r="282">
@@ -4913,16 +4934,16 @@
         <v>1</v>
       </c>
       <c r="B282" s="0">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="C282" s="0">
-        <v>0.91284400635778595</v>
+        <v>0.92499255133343627</v>
       </c>
       <c r="D282" s="0" t="s">
         <v>8</v>
       </c>
       <c r="E282" s="0">
-        <v>130.51189747515053</v>
+        <v>136.14410749361414</v>
       </c>
     </row>
     <row r="283">
@@ -4930,16 +4951,16 @@
         <v>1</v>
       </c>
       <c r="B283" s="0">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="C283" s="0">
-        <v>0.91284400635778595</v>
+        <v>0.92499255133343627</v>
       </c>
       <c r="D283" s="0" t="s">
         <v>6</v>
       </c>
       <c r="E283" s="0">
-        <v>121.22429344750975</v>
+        <v>102.88354063576195</v>
       </c>
     </row>
     <row r="284">
@@ -4947,16 +4968,16 @@
         <v>1</v>
       </c>
       <c r="B284" s="0">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="C284" s="0">
-        <v>0.91284400635778595</v>
+        <v>0.92499255133343627</v>
       </c>
       <c r="D284" s="0" t="s">
         <v>7</v>
       </c>
       <c r="E284" s="0">
-        <v>104.60861052394708</v>
+        <v>93.767215260389051</v>
       </c>
     </row>
     <row r="285">
@@ -4964,16 +4985,16 @@
         <v>1</v>
       </c>
       <c r="B285" s="0">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="C285" s="0">
-        <v>0.91284400635778595</v>
+        <v>0.92499255133343627</v>
       </c>
       <c r="D285" s="0" t="s">
         <v>9</v>
       </c>
       <c r="E285" s="0">
-        <v>88.127129724252512</v>
+        <v>54.304589232895587</v>
       </c>
     </row>
     <row r="286">
@@ -4981,16 +5002,16 @@
         <v>1</v>
       </c>
       <c r="B286" s="0">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="C286" s="0">
-        <v>0.91284400635778595</v>
+        <v>0.92499255133343627</v>
       </c>
       <c r="D286" s="0" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="E286" s="0">
-        <v>38.025199354674079</v>
+        <v>25.159774398462424</v>
       </c>
     </row>
     <row r="287">
@@ -4998,16 +5019,16 @@
         <v>1</v>
       </c>
       <c r="B287" s="0">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="C287" s="0">
-        <v>0.91284400635778595</v>
+        <v>0.92499255133343627</v>
       </c>
       <c r="D287" s="0" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="E287" s="0">
-        <v>4.2360418704405705</v>
+        <v>20.531138867899468</v>
       </c>
     </row>
     <row r="288">
@@ -5015,16 +5036,16 @@
         <v>1</v>
       </c>
       <c r="B288" s="0">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="C288" s="0">
-        <v>0.91284400635778595</v>
+        <v>0.92499255133343627</v>
       </c>
       <c r="D288" s="0" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E288" s="0">
-        <v>3.924753350825859</v>
+        <v>15.250508938437862</v>
       </c>
     </row>
     <row r="289">
@@ -5032,16 +5053,16 @@
         <v>1</v>
       </c>
       <c r="B289" s="0">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="C289" s="0">
-        <v>0.91284400635778595</v>
+        <v>0.92499255133343627</v>
       </c>
       <c r="D289" s="0" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="E289" s="0">
-        <v>3.6816048244599711</v>
+        <v>4.8113462716053768</v>
       </c>
     </row>
     <row r="290">
@@ -5049,16 +5070,16 @@
         <v>1</v>
       </c>
       <c r="B290" s="0">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="C290" s="0">
-        <v>0.91284400635778595</v>
+        <v>0.92499255133343627</v>
       </c>
       <c r="D290" s="0" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E290" s="0">
-        <v>3.2871223808951981</v>
+        <v>2.2475162219645322</v>
       </c>
     </row>
     <row r="291">
@@ -5066,16 +5087,16 @@
         <v>1</v>
       </c>
       <c r="B291" s="0">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="C291" s="0">
-        <v>0.91284400635778595</v>
+        <v>0.92499255133343627</v>
       </c>
       <c r="D291" s="0" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E291" s="0">
-        <v>3.0814721855072866</v>
+        <v>2.2466600912333932</v>
       </c>
     </row>
     <row r="292">
@@ -5083,16 +5104,16 @@
         <v>1</v>
       </c>
       <c r="B292" s="0">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="C292" s="0">
-        <v>0.93177970092505336</v>
+        <v>0.92236330384526655</v>
       </c>
       <c r="D292" s="0" t="s">
         <v>8</v>
       </c>
       <c r="E292" s="0">
-        <v>135.90013718005594</v>
+        <v>122.359926541324</v>
       </c>
     </row>
     <row r="293">
@@ -5100,16 +5121,16 @@
         <v>1</v>
       </c>
       <c r="B293" s="0">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="C293" s="0">
-        <v>0.93177970092505336</v>
+        <v>0.92236330384526655</v>
       </c>
       <c r="D293" s="0" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E293" s="0">
-        <v>100.36745944467384</v>
+        <v>92.393383144582074</v>
       </c>
     </row>
     <row r="294">
@@ -5117,16 +5138,16 @@
         <v>1</v>
       </c>
       <c r="B294" s="0">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="C294" s="0">
-        <v>0.93177970092505336</v>
+        <v>0.92236330384526655</v>
       </c>
       <c r="D294" s="0" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E294" s="0">
-        <v>96.057681587341989</v>
+        <v>89.339699764963413</v>
       </c>
     </row>
     <row r="295">
@@ -5134,16 +5155,16 @@
         <v>1</v>
       </c>
       <c r="B295" s="0">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="C295" s="0">
-        <v>0.93177970092505336</v>
+        <v>0.92236330384526655</v>
       </c>
       <c r="D295" s="0" t="s">
         <v>9</v>
       </c>
       <c r="E295" s="0">
-        <v>67.276822490535821</v>
+        <v>68.531862745655715</v>
       </c>
     </row>
     <row r="296">
@@ -5151,16 +5172,16 @@
         <v>1</v>
       </c>
       <c r="B296" s="0">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="C296" s="0">
-        <v>0.93177970092505336</v>
+        <v>0.92236330384526655</v>
       </c>
       <c r="D296" s="0" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="E296" s="0">
-        <v>31.439079515537358</v>
+        <v>37.702909605984239</v>
       </c>
     </row>
     <row r="297">
@@ -5168,16 +5189,16 @@
         <v>1</v>
       </c>
       <c r="B297" s="0">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="C297" s="0">
-        <v>0.93177970092505336</v>
+        <v>0.92236330384526655</v>
       </c>
       <c r="D297" s="0" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="E297" s="0">
-        <v>5.7636866506906816</v>
+        <v>16.420159514242378</v>
       </c>
     </row>
     <row r="298">
@@ -5185,16 +5206,16 @@
         <v>1</v>
       </c>
       <c r="B298" s="0">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="C298" s="0">
-        <v>0.93177970092505336</v>
+        <v>0.92236330384526655</v>
       </c>
       <c r="D298" s="0" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E298" s="0">
-        <v>5.3319826886413964</v>
+        <v>13.213584720628026</v>
       </c>
     </row>
     <row r="299">
@@ -5202,16 +5223,16 @@
         <v>1</v>
       </c>
       <c r="B299" s="0">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="C299" s="0">
-        <v>0.93177970092505336</v>
+        <v>0.92236330384526655</v>
       </c>
       <c r="D299" s="0" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="E299" s="0">
-        <v>3.9384236612944377</v>
+        <v>8.8411216637344037</v>
       </c>
     </row>
     <row r="300">
@@ -5219,16 +5240,16 @@
         <v>1</v>
       </c>
       <c r="B300" s="0">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="C300" s="0">
-        <v>0.93177970092505336</v>
+        <v>0.92236330384526655</v>
       </c>
       <c r="D300" s="0" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E300" s="0">
-        <v>3.0974704851303603</v>
+        <v>2.6783598665375945</v>
       </c>
     </row>
     <row r="301">
@@ -5236,16 +5257,16 @@
         <v>1</v>
       </c>
       <c r="B301" s="0">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="C301" s="0">
-        <v>0.93177970092505336</v>
+        <v>0.92236330384526655</v>
       </c>
       <c r="D301" s="0" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="E301" s="0">
-        <v>2.8076045978457733</v>
+        <v>2.2840929543186106</v>
       </c>
     </row>
     <row r="302">
@@ -5253,16 +5274,16 @@
         <v>1</v>
       </c>
       <c r="B302" s="0">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="C302" s="0">
-        <v>0.90983687489468412</v>
+        <v>0.92435557627092879</v>
       </c>
       <c r="D302" s="0" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E302" s="0">
-        <v>142.32791426308788</v>
+        <v>102.51593973251229</v>
       </c>
     </row>
     <row r="303">
@@ -5270,16 +5291,16 @@
         <v>1</v>
       </c>
       <c r="B303" s="0">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="C303" s="0">
-        <v>0.90983687489468412</v>
+        <v>0.92435557627092879</v>
       </c>
       <c r="D303" s="0" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E303" s="0">
-        <v>118.24510209284712</v>
+        <v>96.989009773275555</v>
       </c>
     </row>
     <row r="304">
@@ -5287,16 +5308,16 @@
         <v>1</v>
       </c>
       <c r="B304" s="0">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="C304" s="0">
-        <v>0.90983687489468412</v>
+        <v>0.92435557627092879</v>
       </c>
       <c r="D304" s="0" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E304" s="0">
-        <v>112.5339829180197</v>
+        <v>86.673142163863389</v>
       </c>
     </row>
     <row r="305">
@@ -5304,16 +5325,16 @@
         <v>1</v>
       </c>
       <c r="B305" s="0">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="C305" s="0">
-        <v>0.90983687489468412</v>
+        <v>0.92435557627092879</v>
       </c>
       <c r="D305" s="0" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E305" s="0">
-        <v>66.342075060540182</v>
+        <v>79.020696801185338</v>
       </c>
     </row>
     <row r="306">
@@ -5321,16 +5342,16 @@
         <v>1</v>
       </c>
       <c r="B306" s="0">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="C306" s="0">
-        <v>0.90983687489468412</v>
+        <v>0.92435557627092879</v>
       </c>
       <c r="D306" s="0" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="E306" s="0">
-        <v>32.440619063664364</v>
+        <v>38.303916296204697</v>
       </c>
     </row>
     <row r="307">
@@ -5338,16 +5359,16 @@
         <v>1</v>
       </c>
       <c r="B307" s="0">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="C307" s="0">
-        <v>0.90983687489468412</v>
+        <v>0.92435557627092879</v>
       </c>
       <c r="D307" s="0" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="E307" s="0">
-        <v>3.5622059115291278</v>
+        <v>22.65748390944486</v>
       </c>
     </row>
     <row r="308">
@@ -5355,16 +5376,16 @@
         <v>1</v>
       </c>
       <c r="B308" s="0">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="C308" s="0">
-        <v>0.90983687489468412</v>
+        <v>0.92435557627092879</v>
       </c>
       <c r="D308" s="0" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E308" s="0">
-        <v>3.5091847701940342</v>
+        <v>17.217906706384912</v>
       </c>
     </row>
     <row r="309">
@@ -5372,16 +5393,16 @@
         <v>1</v>
       </c>
       <c r="B309" s="0">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="C309" s="0">
-        <v>0.90983687489468412</v>
+        <v>0.92435557627092879</v>
       </c>
       <c r="D309" s="0" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="E309" s="0">
-        <v>3.3826739662458176</v>
+        <v>4.6893793011129565</v>
       </c>
     </row>
     <row r="310">
@@ -5389,16 +5410,16 @@
         <v>1</v>
       </c>
       <c r="B310" s="0">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="C310" s="0">
-        <v>0.90983687489468412</v>
+        <v>0.92435557627092879</v>
       </c>
       <c r="D310" s="0" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E310" s="0">
-        <v>3.3010242379699064</v>
+        <v>2.1597212267740091</v>
       </c>
     </row>
     <row r="311">
@@ -5406,16 +5427,16 @@
         <v>1</v>
       </c>
       <c r="B311" s="0">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="C311" s="0">
-        <v>0.90983687489468412</v>
+        <v>0.92435557627092879</v>
       </c>
       <c r="D311" s="0" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E311" s="0">
-        <v>2.8665413022201354</v>
+        <v>2.0004234171303437</v>
       </c>
     </row>
     <row r="312">
@@ -5423,16 +5444,16 @@
         <v>1</v>
       </c>
       <c r="B312" s="0">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="C312" s="0">
-        <v>0.90262896168546702</v>
+        <v>0.91486236047504477</v>
       </c>
       <c r="D312" s="0" t="s">
         <v>8</v>
       </c>
       <c r="E312" s="0">
-        <v>132.90153308467265</v>
+        <v>107.02321409570587</v>
       </c>
     </row>
     <row r="313">
@@ -5440,16 +5461,16 @@
         <v>1</v>
       </c>
       <c r="B313" s="0">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="C313" s="0">
-        <v>0.90262896168546702</v>
+        <v>0.91486236047504477</v>
       </c>
       <c r="D313" s="0" t="s">
         <v>6</v>
       </c>
       <c r="E313" s="0">
-        <v>113.2530351138298</v>
+        <v>100.51626066802262</v>
       </c>
     </row>
     <row r="314">
@@ -5457,16 +5478,16 @@
         <v>1</v>
       </c>
       <c r="B314" s="0">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="C314" s="0">
-        <v>0.90262896168546702</v>
+        <v>0.91486236047504477</v>
       </c>
       <c r="D314" s="0" t="s">
         <v>7</v>
       </c>
       <c r="E314" s="0">
-        <v>112.64229412884443</v>
+        <v>93.42857462118485</v>
       </c>
     </row>
     <row r="315">
@@ -5474,16 +5495,16 @@
         <v>1</v>
       </c>
       <c r="B315" s="0">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="C315" s="0">
-        <v>0.90262896168546702</v>
+        <v>0.91486236047504477</v>
       </c>
       <c r="D315" s="0" t="s">
         <v>9</v>
       </c>
       <c r="E315" s="0">
-        <v>77.480731675043273</v>
+        <v>69.473808205197884</v>
       </c>
     </row>
     <row r="316">
@@ -5491,16 +5512,16 @@
         <v>1</v>
       </c>
       <c r="B316" s="0">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="C316" s="0">
-        <v>0.90262896168546702</v>
+        <v>0.91486236047504477</v>
       </c>
       <c r="D316" s="0" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="E316" s="0">
-        <v>31.830284434580413</v>
+        <v>29.166864854863107</v>
       </c>
     </row>
     <row r="317">
@@ -5508,16 +5529,16 @@
         <v>1</v>
       </c>
       <c r="B317" s="0">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="C317" s="0">
-        <v>0.90262896168546702</v>
+        <v>0.91486236047504477</v>
       </c>
       <c r="D317" s="0" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="E317" s="0">
-        <v>3.4466062299271476</v>
+        <v>27.09975817116829</v>
       </c>
     </row>
     <row r="318">
@@ -5525,16 +5546,16 @@
         <v>1</v>
       </c>
       <c r="B318" s="0">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="C318" s="0">
-        <v>0.90262896168546702</v>
+        <v>0.91486236047504477</v>
       </c>
       <c r="D318" s="0" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="E318" s="0">
-        <v>3.1051036863827837</v>
+        <v>15.877365692932647</v>
       </c>
     </row>
     <row r="319">
@@ -5542,16 +5563,16 @@
         <v>1</v>
       </c>
       <c r="B319" s="0">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="C319" s="0">
-        <v>0.90262896168546702</v>
+        <v>0.91486236047504477</v>
       </c>
       <c r="D319" s="0" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E319" s="0">
-        <v>2.7872672836967451</v>
+        <v>11.629989519422933</v>
       </c>
     </row>
     <row r="320">
@@ -5559,16 +5580,16 @@
         <v>1</v>
       </c>
       <c r="B320" s="0">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="C320" s="0">
-        <v>0.90262896168546702</v>
+        <v>0.91486236047504477</v>
       </c>
       <c r="D320" s="0" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E320" s="0">
-        <v>2.7461514666600477</v>
+        <v>2.463459140545516</v>
       </c>
     </row>
     <row r="321">
@@ -5576,16 +5597,16 @@
         <v>1</v>
       </c>
       <c r="B321" s="0">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="C321" s="0">
-        <v>0.90262896168546702</v>
+        <v>0.91486236047504477</v>
       </c>
       <c r="D321" s="0" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E321" s="0">
-        <v>2.6485267655801743</v>
+        <v>1.9639459294237349</v>
       </c>
     </row>
     <row r="322">
